--- a/research/traditional_assets/database/data/mauritius/mauritius_computer_services.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_computer_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1178857985050961</v>
+        <v>0.1177472198073385</v>
       </c>
       <c r="C2">
-        <v>20.50418706128382</v>
+        <v>20.32212708974734</v>
       </c>
       <c r="D2">
-        <v>14.28418706128382</v>
+        <v>14.30660708974734</v>
       </c>
       <c r="E2">
-        <v>-0.648</v>
+        <v>-0.44352</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.20448</v>
       </c>
       <c r="G2">
         <v>6.22</v>
@@ -1439,28 +1439,28 @@
         <v>1.64</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.010285344</v>
       </c>
       <c r="N2">
-        <v>1.64</v>
+        <v>1.629714656</v>
       </c>
       <c r="O2">
-        <v>0.246</v>
+        <v>0.2444571984</v>
       </c>
       <c r="P2">
-        <v>1.394</v>
+        <v>1.3852574576</v>
       </c>
       <c r="Q2">
-        <v>1.514</v>
+        <v>1.5052574576</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1178857985050961</v>
+        <v>0.1185047169771096</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763957</v>
+        <v>1.000807795607658</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>159.4501846510919</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1177472198073385</v>
+        <v>0.1176086411095809</v>
       </c>
       <c r="C3">
-        <v>20.32212708974734</v>
+        <v>20.14013760844888</v>
       </c>
       <c r="D3">
-        <v>14.30660708974734</v>
+        <v>14.32909760844888</v>
       </c>
       <c r="E3">
-        <v>-0.44352</v>
+        <v>-0.23904</v>
       </c>
       <c r="F3">
-        <v>0.20448</v>
+        <v>0.40896</v>
       </c>
       <c r="G3">
         <v>6.22</v>
@@ -1521,28 +1521,28 @@
         <v>1.64</v>
       </c>
       <c r="M3">
-        <v>0.010285344</v>
+        <v>0.020570688</v>
       </c>
       <c r="N3">
-        <v>1.629714656</v>
+        <v>1.619429312</v>
       </c>
       <c r="O3">
-        <v>0.2444571984</v>
+        <v>0.2429143968</v>
       </c>
       <c r="P3">
-        <v>1.3852574576</v>
+        <v>1.3765149152</v>
       </c>
       <c r="Q3">
-        <v>1.5052574576</v>
+        <v>1.4965149152</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1185047169771096</v>
+        <v>0.1191362664383478</v>
       </c>
       <c r="T3">
-        <v>1.000807795607658</v>
+        <v>1.009501311659966</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>159.4501846510919</v>
+        <v>79.72509232554593</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1176086411095809</v>
+        <v>0.1174700624118232</v>
       </c>
       <c r="C4">
-        <v>20.14013760844888</v>
+        <v>19.95821895035168</v>
       </c>
       <c r="D4">
-        <v>14.32909760844888</v>
+        <v>14.35165895035168</v>
       </c>
       <c r="E4">
-        <v>-0.23904</v>
+        <v>-0.03456000000000004</v>
       </c>
       <c r="F4">
-        <v>0.40896</v>
+        <v>0.61344</v>
       </c>
       <c r="G4">
         <v>6.22</v>
@@ -1603,28 +1603,28 @@
         <v>1.64</v>
       </c>
       <c r="M4">
-        <v>0.020570688</v>
+        <v>0.030856032</v>
       </c>
       <c r="N4">
-        <v>1.619429312</v>
+        <v>1.609143968</v>
       </c>
       <c r="O4">
-        <v>0.2429143968</v>
+        <v>0.2413715952</v>
       </c>
       <c r="P4">
-        <v>1.3765149152</v>
+        <v>1.3677723728</v>
       </c>
       <c r="Q4">
-        <v>1.4965149152</v>
+        <v>1.4877723728</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1191362664383478</v>
+        <v>0.1197808375379621</v>
       </c>
       <c r="T4">
-        <v>1.009501311659966</v>
+        <v>1.01837407546593</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>79.72509232554593</v>
+        <v>53.15006155036396</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1174700624118232</v>
+        <v>0.1173314837140656</v>
       </c>
       <c r="C5">
-        <v>19.95821895035168</v>
+        <v>19.77637145051935</v>
       </c>
       <c r="D5">
-        <v>14.35165895035168</v>
+        <v>14.37429145051935</v>
       </c>
       <c r="E5">
-        <v>-0.03456000000000004</v>
+        <v>0.16992</v>
       </c>
       <c r="F5">
-        <v>0.61344</v>
+        <v>0.81792</v>
       </c>
       <c r="G5">
         <v>6.22</v>
@@ -1685,28 +1685,28 @@
         <v>1.64</v>
       </c>
       <c r="M5">
-        <v>0.030856032</v>
+        <v>0.041141376</v>
       </c>
       <c r="N5">
-        <v>1.609143968</v>
+        <v>1.598858624</v>
       </c>
       <c r="O5">
-        <v>0.2413715952</v>
+        <v>0.2398287936</v>
       </c>
       <c r="P5">
-        <v>1.3677723728</v>
+        <v>1.3590298304</v>
       </c>
       <c r="Q5">
-        <v>1.4877723728</v>
+        <v>1.4790298304</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1197808375379621</v>
+        <v>0.1204388372021516</v>
       </c>
       <c r="T5">
-        <v>1.01837407546593</v>
+        <v>1.027431688517851</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>53.15006155036396</v>
+        <v>39.86254616277297</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1173314837140656</v>
+        <v>0.1171929050163079</v>
       </c>
       <c r="C6">
-        <v>19.77637145051935</v>
+        <v>19.59459544613238</v>
       </c>
       <c r="D6">
-        <v>14.37429145051935</v>
+        <v>14.39699544613238</v>
       </c>
       <c r="E6">
-        <v>0.16992</v>
+        <v>0.3744</v>
       </c>
       <c r="F6">
-        <v>0.81792</v>
+        <v>1.0224</v>
       </c>
       <c r="G6">
         <v>6.22</v>
@@ -1767,28 +1767,28 @@
         <v>1.64</v>
       </c>
       <c r="M6">
-        <v>0.041141376</v>
+        <v>0.05142672</v>
       </c>
       <c r="N6">
-        <v>1.598858624</v>
+        <v>1.58857328</v>
       </c>
       <c r="O6">
-        <v>0.2398287936</v>
+        <v>0.238285992</v>
       </c>
       <c r="P6">
-        <v>1.3590298304</v>
+        <v>1.350287288</v>
       </c>
       <c r="Q6">
-        <v>1.4790298304</v>
+        <v>1.470287288</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1204388372021516</v>
+        <v>0.1211106894908505</v>
       </c>
       <c r="T6">
-        <v>1.027431688517851</v>
+        <v>1.03667998816034</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>39.86254616277297</v>
+        <v>31.89003693021838</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1171929050163079</v>
+        <v>0.1170543263185503</v>
       </c>
       <c r="C7">
-        <v>19.59459544613238</v>
+        <v>19.41289127650493</v>
       </c>
       <c r="D7">
-        <v>14.39699544613238</v>
+        <v>14.41977127650493</v>
       </c>
       <c r="E7">
-        <v>0.3744</v>
+        <v>0.5788800000000002</v>
       </c>
       <c r="F7">
-        <v>1.0224</v>
+        <v>1.22688</v>
       </c>
       <c r="G7">
         <v>6.22</v>
@@ -1849,28 +1849,28 @@
         <v>1.64</v>
       </c>
       <c r="M7">
-        <v>0.05142672</v>
+        <v>0.061712064</v>
       </c>
       <c r="N7">
-        <v>1.58857328</v>
+        <v>1.578287936</v>
       </c>
       <c r="O7">
-        <v>0.238285992</v>
+        <v>0.2367431904</v>
       </c>
       <c r="P7">
-        <v>1.350287288</v>
+        <v>1.3415447456</v>
       </c>
       <c r="Q7">
-        <v>1.470287288</v>
+        <v>1.4615447456</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1211106894908505</v>
+        <v>0.1217968365090961</v>
       </c>
       <c r="T7">
-        <v>1.03667998816034</v>
+        <v>1.046125060135647</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>31.89003693021838</v>
+        <v>26.57503077518198</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1170543263185503</v>
+        <v>0.1169157476207927</v>
       </c>
       <c r="C8">
-        <v>19.41289127650493</v>
+        <v>19.23125928310172</v>
       </c>
       <c r="D8">
-        <v>14.41977127650493</v>
+        <v>14.44261928310172</v>
       </c>
       <c r="E8">
-        <v>0.57888</v>
+        <v>0.7833599999999999</v>
       </c>
       <c r="F8">
-        <v>1.22688</v>
+        <v>1.43136</v>
       </c>
       <c r="G8">
         <v>6.22</v>
@@ -1931,28 +1931,28 @@
         <v>1.64</v>
       </c>
       <c r="M8">
-        <v>0.061712064</v>
+        <v>0.071997408</v>
       </c>
       <c r="N8">
-        <v>1.578287936</v>
+        <v>1.568002592</v>
       </c>
       <c r="O8">
-        <v>0.2367431904</v>
+        <v>0.2352003888</v>
       </c>
       <c r="P8">
-        <v>1.3415447456</v>
+        <v>1.3328022032</v>
       </c>
       <c r="Q8">
-        <v>1.4615447456</v>
+        <v>1.4528022032</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1217968365090961</v>
+        <v>0.1224977393771964</v>
       </c>
       <c r="T8">
-        <v>1.046125060135647</v>
+        <v>1.05577325193838</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>26.57503077518198</v>
+        <v>22.77859780729884</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1169157476207927</v>
+        <v>0.116777168923035</v>
       </c>
       <c r="C9">
-        <v>19.23125928310172</v>
+        <v>19.04969980955511</v>
       </c>
       <c r="D9">
-        <v>14.44261928310173</v>
+        <v>14.46553980955511</v>
       </c>
       <c r="E9">
-        <v>0.7833600000000002</v>
+        <v>0.9878399999999999</v>
       </c>
       <c r="F9">
-        <v>1.43136</v>
+        <v>1.63584</v>
       </c>
       <c r="G9">
         <v>6.22</v>
@@ -2013,28 +2013,28 @@
         <v>1.64</v>
       </c>
       <c r="M9">
-        <v>0.07199740800000001</v>
+        <v>0.082282752</v>
       </c>
       <c r="N9">
-        <v>1.568002592</v>
+        <v>1.557717248</v>
       </c>
       <c r="O9">
-        <v>0.2352003888</v>
+        <v>0.2336575872</v>
       </c>
       <c r="P9">
-        <v>1.3328022032</v>
+        <v>1.3240596608</v>
       </c>
       <c r="Q9">
-        <v>1.4528022032</v>
+        <v>1.4440596608</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1224977393771964</v>
+        <v>0.1232138792641685</v>
       </c>
       <c r="T9">
-        <v>1.05577325193838</v>
+        <v>1.065631187041173</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>22.77859780729883</v>
+        <v>19.93127308138648</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.116777168923035</v>
+        <v>0.1166385902252774</v>
       </c>
       <c r="C10">
-        <v>19.04969980955511</v>
+        <v>18.8682132016823</v>
       </c>
       <c r="D10">
-        <v>14.46553980955511</v>
+        <v>14.4885332016823</v>
       </c>
       <c r="E10">
-        <v>0.9878399999999999</v>
+        <v>1.19232</v>
       </c>
       <c r="F10">
-        <v>1.63584</v>
+        <v>1.84032</v>
       </c>
       <c r="G10">
         <v>6.22</v>
@@ -2095,28 +2095,28 @@
         <v>1.64</v>
       </c>
       <c r="M10">
-        <v>0.082282752</v>
+        <v>0.09256809599999999</v>
       </c>
       <c r="N10">
-        <v>1.557717248</v>
+        <v>1.547431904</v>
       </c>
       <c r="O10">
-        <v>0.2336575872</v>
+        <v>0.2321147856</v>
       </c>
       <c r="P10">
-        <v>1.3240596608</v>
+        <v>1.3153171184</v>
       </c>
       <c r="Q10">
-        <v>1.4440596608</v>
+        <v>1.4353171184</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1232138792641685</v>
+        <v>0.1239457584893158</v>
       </c>
       <c r="T10">
-        <v>1.065631187041173</v>
+        <v>1.075705780058312</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>19.93127308138648</v>
+        <v>17.71668718345466</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1166385902252774</v>
+        <v>0.1165000115275197</v>
       </c>
       <c r="C11">
-        <v>18.8682132016823</v>
+        <v>18.68679980750272</v>
       </c>
       <c r="D11">
-        <v>14.4885332016823</v>
+        <v>14.51159980750272</v>
       </c>
       <c r="E11">
-        <v>1.19232</v>
+        <v>1.3968</v>
       </c>
       <c r="F11">
-        <v>1.84032</v>
+        <v>2.0448</v>
       </c>
       <c r="G11">
         <v>6.22</v>
@@ -2177,28 +2177,28 @@
         <v>1.64</v>
       </c>
       <c r="M11">
-        <v>0.09256809599999999</v>
+        <v>0.10285344</v>
       </c>
       <c r="N11">
-        <v>1.547431904</v>
+        <v>1.53714656</v>
       </c>
       <c r="O11">
-        <v>0.2321147856</v>
+        <v>0.230571984</v>
       </c>
       <c r="P11">
-        <v>1.3153171184</v>
+        <v>1.306574576</v>
       </c>
       <c r="Q11">
-        <v>1.4353171184</v>
+        <v>1.426574576</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1239457584893158</v>
+        <v>0.1246939016972441</v>
       </c>
       <c r="T11">
-        <v>1.075705780058312</v>
+        <v>1.086004252920278</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>17.71668718345466</v>
+        <v>15.94501846510919</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1165000115275197</v>
+        <v>0.1163614328297621</v>
       </c>
       <c r="C12">
-        <v>18.68679980750272</v>
+        <v>18.50545997725564</v>
       </c>
       <c r="D12">
-        <v>14.51159980750272</v>
+        <v>14.53473997725563</v>
       </c>
       <c r="E12">
-        <v>1.3968</v>
+        <v>1.60128</v>
       </c>
       <c r="F12">
-        <v>2.0448</v>
+        <v>2.24928</v>
       </c>
       <c r="G12">
         <v>6.22</v>
@@ -2259,28 +2259,28 @@
         <v>1.64</v>
       </c>
       <c r="M12">
-        <v>0.10285344</v>
+        <v>0.113138784</v>
       </c>
       <c r="N12">
-        <v>1.53714656</v>
+        <v>1.526861216</v>
       </c>
       <c r="O12">
-        <v>0.230571984</v>
+        <v>0.2290291824</v>
       </c>
       <c r="P12">
-        <v>1.306574576</v>
+        <v>1.2978320336</v>
       </c>
       <c r="Q12">
-        <v>1.426574576</v>
+        <v>1.4178320336</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1246939016972441</v>
+        <v>0.1254588571120922</v>
       </c>
       <c r="T12">
-        <v>1.086004252920278</v>
+        <v>1.096534152138691</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>15.94501846510919</v>
+        <v>14.49547133191744</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1163614328297621</v>
+        <v>0.1162228541320044</v>
       </c>
       <c r="C13">
-        <v>18.50545997725564</v>
+        <v>18.32419406341783</v>
       </c>
       <c r="D13">
-        <v>14.53473997725563</v>
+        <v>14.55795406341783</v>
       </c>
       <c r="E13">
-        <v>1.60128</v>
+        <v>1.80576</v>
       </c>
       <c r="F13">
-        <v>2.24928</v>
+        <v>2.45376</v>
       </c>
       <c r="G13">
         <v>6.22</v>
@@ -2341,28 +2341,28 @@
         <v>1.64</v>
       </c>
       <c r="M13">
-        <v>0.113138784</v>
+        <v>0.123424128</v>
       </c>
       <c r="N13">
-        <v>1.526861216</v>
+        <v>1.516575872</v>
       </c>
       <c r="O13">
-        <v>0.2290291824</v>
+        <v>0.2274863808</v>
       </c>
       <c r="P13">
-        <v>1.2978320336</v>
+        <v>1.2890894912</v>
       </c>
       <c r="Q13">
-        <v>1.4178320336</v>
+        <v>1.4090894912</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1254588571120922</v>
+        <v>0.1262411978772777</v>
       </c>
       <c r="T13">
-        <v>1.096534152138691</v>
+        <v>1.107303367248432</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>14.49547133191744</v>
+        <v>13.28751538759099</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1162228541320044</v>
+        <v>0.1162500254342468</v>
       </c>
       <c r="C14">
-        <v>18.32419406341783</v>
+        <v>18.11515660549595</v>
       </c>
       <c r="D14">
-        <v>14.55795406341783</v>
+        <v>14.55339660549595</v>
       </c>
       <c r="E14">
-        <v>1.80576</v>
+        <v>2.01024</v>
       </c>
       <c r="F14">
-        <v>2.45376</v>
+        <v>2.65824</v>
       </c>
       <c r="G14">
         <v>6.22</v>
@@ -2423,45 +2423,45 @@
         <v>1.64</v>
       </c>
       <c r="M14">
-        <v>0.123424128</v>
+        <v>0.137696832</v>
       </c>
       <c r="N14">
-        <v>1.516575872</v>
+        <v>1.502303168</v>
       </c>
       <c r="O14">
-        <v>0.2274863808</v>
+        <v>0.2253454752</v>
       </c>
       <c r="P14">
-        <v>1.2890894912</v>
+        <v>1.2769576928</v>
       </c>
       <c r="Q14">
-        <v>1.4090894912</v>
+        <v>1.3969576928</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1262411978772777</v>
+        <v>0.12704152348764</v>
       </c>
       <c r="T14">
-        <v>1.107303367248432</v>
+        <v>1.118320150521616</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.15</v>
       </c>
       <c r="W14">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.28751538759099</v>
+        <v>11.91022317782881</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1162500254342468</v>
+        <v>0.1161241967364891</v>
       </c>
       <c r="C15">
-        <v>18.11515660549595</v>
+        <v>17.93180594927838</v>
       </c>
       <c r="D15">
-        <v>14.55339660549595</v>
+        <v>14.57452594927838</v>
       </c>
       <c r="E15">
-        <v>2.01024</v>
+        <v>2.21472</v>
       </c>
       <c r="F15">
-        <v>2.65824</v>
+        <v>2.86272</v>
       </c>
       <c r="G15">
         <v>6.22</v>
@@ -2505,28 +2505,28 @@
         <v>1.64</v>
       </c>
       <c r="M15">
-        <v>0.137696832</v>
+        <v>0.148288896</v>
       </c>
       <c r="N15">
-        <v>1.502303168</v>
+        <v>1.491711104</v>
       </c>
       <c r="O15">
-        <v>0.2253454752</v>
+        <v>0.2237566656</v>
       </c>
       <c r="P15">
-        <v>1.2769576928</v>
+        <v>1.2679544384</v>
       </c>
       <c r="Q15">
-        <v>1.3969576928</v>
+        <v>1.3879544384</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.12704152348764</v>
+        <v>0.127860461321499</v>
       </c>
       <c r="T15">
-        <v>1.118320150521616</v>
+        <v>1.129593138056967</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.91022317782881</v>
+        <v>11.05949295084104</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1161241967364891</v>
+        <v>0.1159983680387315</v>
       </c>
       <c r="C16">
-        <v>17.93180594927838</v>
+        <v>17.74851673552681</v>
       </c>
       <c r="D16">
-        <v>14.57452594927838</v>
+        <v>14.59571673552681</v>
       </c>
       <c r="E16">
-        <v>2.21472</v>
+        <v>2.4192</v>
       </c>
       <c r="F16">
-        <v>2.86272</v>
+        <v>3.067200000000001</v>
       </c>
       <c r="G16">
         <v>6.22</v>
@@ -2587,28 +2587,28 @@
         <v>1.64</v>
       </c>
       <c r="M16">
-        <v>0.148288896</v>
+        <v>0.15888096</v>
       </c>
       <c r="N16">
-        <v>1.491711104</v>
+        <v>1.48111904</v>
       </c>
       <c r="O16">
-        <v>0.2237566656</v>
+        <v>0.222167856</v>
       </c>
       <c r="P16">
-        <v>1.2679544384</v>
+        <v>1.258951184</v>
       </c>
       <c r="Q16">
-        <v>1.3879544384</v>
+        <v>1.378951184</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.127860461321499</v>
+        <v>0.1286986682808606</v>
       </c>
       <c r="T16">
-        <v>1.129593138056967</v>
+        <v>1.141131372357855</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.05949295084104</v>
+        <v>10.32219342078497</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1159983680387315</v>
+        <v>0.1161037393409739</v>
       </c>
       <c r="C17">
-        <v>17.74851673552681</v>
+        <v>17.52628698551927</v>
       </c>
       <c r="D17">
-        <v>14.59571673552681</v>
+        <v>14.57796698551927</v>
       </c>
       <c r="E17">
-        <v>2.4192</v>
+        <v>2.62368</v>
       </c>
       <c r="F17">
-        <v>3.0672</v>
+        <v>3.27168</v>
       </c>
       <c r="G17">
         <v>6.22</v>
@@ -2669,45 +2669,45 @@
         <v>1.64</v>
       </c>
       <c r="M17">
-        <v>0.15888096</v>
+        <v>0.17503488</v>
       </c>
       <c r="N17">
-        <v>1.48111904</v>
+        <v>1.46496512</v>
       </c>
       <c r="O17">
-        <v>0.222167856</v>
+        <v>0.219744768</v>
       </c>
       <c r="P17">
-        <v>1.258951184</v>
+        <v>1.245220352</v>
       </c>
       <c r="Q17">
-        <v>1.378951184</v>
+        <v>1.365220352</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1286986682808606</v>
+        <v>0.1295568325487784</v>
       </c>
       <c r="T17">
-        <v>1.141131372357855</v>
+        <v>1.15294432652305</v>
       </c>
       <c r="U17">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V17">
         <v>0.15</v>
       </c>
       <c r="W17">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>10.32219342078497</v>
+        <v>9.369561084053647</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1161037393409739</v>
+        <v>0.1159923606432162</v>
       </c>
       <c r="C18">
-        <v>17.52628698551927</v>
+        <v>17.3405699811379</v>
       </c>
       <c r="D18">
-        <v>14.57796698551927</v>
+        <v>14.5967299811379</v>
       </c>
       <c r="E18">
-        <v>2.62368</v>
+        <v>2.82816</v>
       </c>
       <c r="F18">
-        <v>3.27168</v>
+        <v>3.47616</v>
       </c>
       <c r="G18">
         <v>6.22</v>
@@ -2751,28 +2751,28 @@
         <v>1.64</v>
       </c>
       <c r="M18">
-        <v>0.17503488</v>
+        <v>0.18597456</v>
       </c>
       <c r="N18">
-        <v>1.46496512</v>
+        <v>1.45402544</v>
       </c>
       <c r="O18">
-        <v>0.219744768</v>
+        <v>0.218103816</v>
       </c>
       <c r="P18">
-        <v>1.245220352</v>
+        <v>1.235921624</v>
       </c>
       <c r="Q18">
-        <v>1.365220352</v>
+        <v>1.355921624</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1295568325487784</v>
+        <v>0.1304356754737545</v>
       </c>
       <c r="T18">
-        <v>1.15294432652305</v>
+        <v>1.165041930186202</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>9.369561084053647</v>
+        <v>8.818410432050491</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1159923606432162</v>
+        <v>0.1158809819454586</v>
       </c>
       <c r="C19">
-        <v>17.3405699811379</v>
+        <v>17.15490133791759</v>
       </c>
       <c r="D19">
-        <v>14.5967299811379</v>
+        <v>14.61554133791759</v>
       </c>
       <c r="E19">
-        <v>2.82816</v>
+        <v>3.03264</v>
       </c>
       <c r="F19">
-        <v>3.47616</v>
+        <v>3.68064</v>
       </c>
       <c r="G19">
         <v>6.22</v>
@@ -2833,28 +2833,28 @@
         <v>1.64</v>
       </c>
       <c r="M19">
-        <v>0.18597456</v>
+        <v>0.19691424</v>
       </c>
       <c r="N19">
-        <v>1.45402544</v>
+        <v>1.44308576</v>
       </c>
       <c r="O19">
-        <v>0.218103816</v>
+        <v>0.2164628639999999</v>
       </c>
       <c r="P19">
-        <v>1.235921624</v>
+        <v>1.226622896</v>
       </c>
       <c r="Q19">
-        <v>1.355921624</v>
+        <v>1.346622896</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1304356754737545</v>
+        <v>0.1313359535920226</v>
       </c>
       <c r="T19">
-        <v>1.165041930186202</v>
+        <v>1.177434597353333</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.818410432050491</v>
+        <v>8.328498741381019</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1158809819454586</v>
+        <v>0.1157696032477009</v>
       </c>
       <c r="C20">
-        <v>17.15490133791759</v>
+        <v>16.96928124307418</v>
       </c>
       <c r="D20">
-        <v>14.61554133791759</v>
+        <v>14.63440124307418</v>
       </c>
       <c r="E20">
-        <v>3.03264</v>
+        <v>3.23712</v>
       </c>
       <c r="F20">
-        <v>3.68064</v>
+        <v>3.88512</v>
       </c>
       <c r="G20">
         <v>6.22</v>
@@ -2915,28 +2915,28 @@
         <v>1.64</v>
       </c>
       <c r="M20">
-        <v>0.19691424</v>
+        <v>0.20785392</v>
       </c>
       <c r="N20">
-        <v>1.44308576</v>
+        <v>1.43214608</v>
       </c>
       <c r="O20">
-        <v>0.216462864</v>
+        <v>0.214821912</v>
       </c>
       <c r="P20">
-        <v>1.226622896</v>
+        <v>1.217324168</v>
       </c>
       <c r="Q20">
-        <v>1.346622896</v>
+        <v>1.337324168</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1313359535920226</v>
+        <v>0.1322584607996307</v>
       </c>
       <c r="T20">
-        <v>1.177434597353333</v>
+        <v>1.190133256302368</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.328498741381019</v>
+        <v>7.890156702360965</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1157696032477009</v>
+        <v>0.1157942245499433</v>
       </c>
       <c r="C21">
-        <v>16.96928124307418</v>
+        <v>16.76062789533191</v>
       </c>
       <c r="D21">
-        <v>14.63440124307418</v>
+        <v>14.63022789533191</v>
       </c>
       <c r="E21">
-        <v>3.23712</v>
+        <v>3.4416</v>
       </c>
       <c r="F21">
-        <v>3.88512</v>
+        <v>4.0896</v>
       </c>
       <c r="G21">
         <v>6.22</v>
@@ -2997,45 +2997,45 @@
         <v>1.64</v>
       </c>
       <c r="M21">
-        <v>0.20785392</v>
+        <v>0.22206528</v>
       </c>
       <c r="N21">
-        <v>1.43214608</v>
+        <v>1.41793472</v>
       </c>
       <c r="O21">
-        <v>0.214821912</v>
+        <v>0.212690208</v>
       </c>
       <c r="P21">
-        <v>1.217324168</v>
+        <v>1.205244512</v>
       </c>
       <c r="Q21">
-        <v>1.337324168</v>
+        <v>1.325244512</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1322584607996307</v>
+        <v>0.1332040306874291</v>
       </c>
       <c r="T21">
-        <v>1.190133256302368</v>
+        <v>1.20314938172513</v>
       </c>
       <c r="U21">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V21">
         <v>0.15</v>
       </c>
       <c r="W21">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y21">
-        <v>7.890156702360965</v>
+        <v>7.385215734760517</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1157942245499433</v>
+        <v>0.1156896458521856</v>
       </c>
       <c r="C22">
-        <v>16.76062789533191</v>
+        <v>16.57389057797169</v>
       </c>
       <c r="D22">
-        <v>14.63022789533191</v>
+        <v>14.64797057797169</v>
       </c>
       <c r="E22">
-        <v>3.4416</v>
+        <v>3.64608</v>
       </c>
       <c r="F22">
-        <v>4.0896</v>
+        <v>4.29408</v>
       </c>
       <c r="G22">
         <v>6.22</v>
@@ -3079,28 +3079,28 @@
         <v>1.64</v>
       </c>
       <c r="M22">
-        <v>0.22206528</v>
+        <v>0.233168544</v>
       </c>
       <c r="N22">
-        <v>1.41793472</v>
+        <v>1.406831456</v>
       </c>
       <c r="O22">
-        <v>0.212690208</v>
+        <v>0.2110247184</v>
       </c>
       <c r="P22">
-        <v>1.205244512</v>
+        <v>1.1958067376</v>
       </c>
       <c r="Q22">
-        <v>1.325244512</v>
+        <v>1.3158067376</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1332040306874291</v>
+        <v>0.1341735390533995</v>
       </c>
       <c r="T22">
-        <v>1.20314938172513</v>
+        <v>1.216495029310493</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.385215734760517</v>
+        <v>7.033538795010016</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1156896458521856</v>
+        <v>0.115585067154428</v>
       </c>
       <c r="C23">
-        <v>16.5738905779717</v>
+        <v>16.3871963474352</v>
       </c>
       <c r="D23">
-        <v>14.6479705779717</v>
+        <v>14.66575634743521</v>
       </c>
       <c r="E23">
-        <v>3.64608</v>
+        <v>3.85056</v>
       </c>
       <c r="F23">
-        <v>4.29408</v>
+        <v>4.49856</v>
       </c>
       <c r="G23">
         <v>6.22</v>
@@ -3161,28 +3161,28 @@
         <v>1.64</v>
       </c>
       <c r="M23">
-        <v>0.233168544</v>
+        <v>0.244271808</v>
       </c>
       <c r="N23">
-        <v>1.406831456</v>
+        <v>1.395728192</v>
       </c>
       <c r="O23">
-        <v>0.2110247184</v>
+        <v>0.2093592288</v>
       </c>
       <c r="P23">
-        <v>1.1958067376</v>
+        <v>1.1863689632</v>
       </c>
       <c r="Q23">
-        <v>1.3158067376</v>
+        <v>1.3063689632</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1341735390533995</v>
+        <v>0.135167906608241</v>
       </c>
       <c r="T23">
-        <v>1.216495029310493</v>
+        <v>1.230182872987788</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.033538795010016</v>
+        <v>6.713832486145924</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.115585067154428</v>
+        <v>0.1154804884566703</v>
       </c>
       <c r="C24">
-        <v>16.3871963474352</v>
+        <v>16.20054536086309</v>
       </c>
       <c r="D24">
-        <v>14.66575634743521</v>
+        <v>14.68358536086309</v>
       </c>
       <c r="E24">
-        <v>3.85056</v>
+        <v>4.055040000000001</v>
       </c>
       <c r="F24">
-        <v>4.49856</v>
+        <v>4.703040000000001</v>
       </c>
       <c r="G24">
         <v>6.22</v>
@@ -3243,28 +3243,28 @@
         <v>1.64</v>
       </c>
       <c r="M24">
-        <v>0.244271808</v>
+        <v>0.255375072</v>
       </c>
       <c r="N24">
-        <v>1.395728192</v>
+        <v>1.384624928</v>
       </c>
       <c r="O24">
-        <v>0.2093592288</v>
+        <v>0.2076937392</v>
       </c>
       <c r="P24">
-        <v>1.1863689632</v>
+        <v>1.1769311888</v>
       </c>
       <c r="Q24">
-        <v>1.3063689632</v>
+        <v>1.2969311888</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.135167906608241</v>
+        <v>0.1361881018917797</v>
       </c>
       <c r="T24">
-        <v>1.230182872987788</v>
+        <v>1.244226245072286</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.713832486145924</v>
+        <v>6.421926725878709</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1154804884566703</v>
+        <v>0.1153759097589127</v>
       </c>
       <c r="C25">
-        <v>16.20054536086309</v>
+        <v>16.0139377761611</v>
       </c>
       <c r="D25">
-        <v>14.68358536086309</v>
+        <v>14.7014577761611</v>
       </c>
       <c r="E25">
-        <v>4.055040000000001</v>
+        <v>4.259520000000001</v>
       </c>
       <c r="F25">
-        <v>4.703040000000001</v>
+        <v>4.907520000000001</v>
       </c>
       <c r="G25">
         <v>6.22</v>
@@ -3325,28 +3325,28 @@
         <v>1.64</v>
       </c>
       <c r="M25">
-        <v>0.255375072</v>
+        <v>0.266478336</v>
       </c>
       <c r="N25">
-        <v>1.384624928</v>
+        <v>1.373521664</v>
       </c>
       <c r="O25">
-        <v>0.2076937392</v>
+        <v>0.2060282496</v>
       </c>
       <c r="P25">
-        <v>1.1769311888</v>
+        <v>1.1674934144</v>
       </c>
       <c r="Q25">
-        <v>1.2969311888</v>
+        <v>1.2874934144</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1361881018917797</v>
+        <v>0.137235144419622</v>
       </c>
       <c r="T25">
-        <v>1.244226245072286</v>
+        <v>1.25863917958006</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.421926725878709</v>
+        <v>6.154346445633763</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1153759097589127</v>
+        <v>0.115483831061155</v>
       </c>
       <c r="C26">
-        <v>16.0139377761611</v>
+        <v>15.79101482907618</v>
       </c>
       <c r="D26">
-        <v>14.7014577761611</v>
+        <v>14.68301482907618</v>
       </c>
       <c r="E26">
-        <v>4.25952</v>
+        <v>4.464</v>
       </c>
       <c r="F26">
-        <v>4.90752</v>
+        <v>5.112</v>
       </c>
       <c r="G26">
         <v>6.22</v>
@@ -3407,45 +3407,45 @@
         <v>1.64</v>
       </c>
       <c r="M26">
-        <v>0.266478336</v>
+        <v>0.2826936</v>
       </c>
       <c r="N26">
-        <v>1.373521664</v>
+        <v>1.3573064</v>
       </c>
       <c r="O26">
-        <v>0.2060282496</v>
+        <v>0.20359596</v>
       </c>
       <c r="P26">
-        <v>1.1674934144</v>
+        <v>1.15371044</v>
       </c>
       <c r="Q26">
-        <v>1.2874934144</v>
+        <v>1.27371044</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.137235144419622</v>
+        <v>0.1383101080815401</v>
       </c>
       <c r="T26">
-        <v>1.25863917958006</v>
+        <v>1.273436459008041</v>
       </c>
       <c r="U26">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V26">
         <v>0.15</v>
       </c>
       <c r="W26">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y26">
-        <v>6.154346445633764</v>
+        <v>5.801334023833578</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.115483831061155</v>
+        <v>0.1153877523633974</v>
       </c>
       <c r="C27">
-        <v>15.79101482907618</v>
+        <v>15.60295170042558</v>
       </c>
       <c r="D27">
-        <v>14.68301482907618</v>
+        <v>14.69943170042558</v>
       </c>
       <c r="E27">
-        <v>4.464</v>
+        <v>4.668480000000001</v>
       </c>
       <c r="F27">
-        <v>5.112</v>
+        <v>5.31648</v>
       </c>
       <c r="G27">
         <v>6.22</v>
@@ -3489,28 +3489,28 @@
         <v>1.64</v>
       </c>
       <c r="M27">
-        <v>0.2826936</v>
+        <v>0.2940013440000001</v>
       </c>
       <c r="N27">
-        <v>1.3573064</v>
+        <v>1.345998656</v>
       </c>
       <c r="O27">
-        <v>0.20359596</v>
+        <v>0.2018997984</v>
       </c>
       <c r="P27">
-        <v>1.15371044</v>
+        <v>1.1440988576</v>
       </c>
       <c r="Q27">
-        <v>1.27371044</v>
+        <v>1.2640988576</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1383101080815401</v>
+        <v>0.1394141248154019</v>
       </c>
       <c r="T27">
-        <v>1.273436459008041</v>
+        <v>1.288633664907049</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.801334023833578</v>
+        <v>5.57820579214767</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1153877523633974</v>
+        <v>0.1152916736656398</v>
       </c>
       <c r="C28">
-        <v>15.60295170042558</v>
+        <v>15.41492532381054</v>
       </c>
       <c r="D28">
-        <v>14.69943170042558</v>
+        <v>14.71588532381055</v>
       </c>
       <c r="E28">
-        <v>4.668480000000001</v>
+        <v>4.872960000000001</v>
       </c>
       <c r="F28">
-        <v>5.31648</v>
+        <v>5.520960000000001</v>
       </c>
       <c r="G28">
         <v>6.22</v>
@@ -3571,28 +3571,28 @@
         <v>1.64</v>
       </c>
       <c r="M28">
-        <v>0.2940013440000001</v>
+        <v>0.3053090880000001</v>
       </c>
       <c r="N28">
-        <v>1.345998656</v>
+        <v>1.334690912</v>
       </c>
       <c r="O28">
-        <v>0.2018997984</v>
+        <v>0.2002036368</v>
       </c>
       <c r="P28">
-        <v>1.1440988576</v>
+        <v>1.1344872752</v>
       </c>
       <c r="Q28">
-        <v>1.2640988576</v>
+        <v>1.2544872752</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1394141248154019</v>
+        <v>0.1405483885830682</v>
       </c>
       <c r="T28">
-        <v>1.288633664907049</v>
+        <v>1.304247232611509</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.57820579214767</v>
+        <v>5.371605577623682</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1152916736656398</v>
+        <v>0.1151955949678821</v>
       </c>
       <c r="C29">
-        <v>15.41492532381054</v>
+        <v>15.22693582278316</v>
       </c>
       <c r="D29">
-        <v>14.71588532381055</v>
+        <v>14.73237582278316</v>
       </c>
       <c r="E29">
-        <v>4.872960000000001</v>
+        <v>5.077440000000001</v>
       </c>
       <c r="F29">
-        <v>5.520960000000001</v>
+        <v>5.725440000000001</v>
       </c>
       <c r="G29">
         <v>6.22</v>
@@ -3653,28 +3653,28 @@
         <v>1.64</v>
       </c>
       <c r="M29">
-        <v>0.3053090880000001</v>
+        <v>0.3166168320000001</v>
       </c>
       <c r="N29">
-        <v>1.334690912</v>
+        <v>1.323383168</v>
       </c>
       <c r="O29">
-        <v>0.2002036368</v>
+        <v>0.1985074752</v>
       </c>
       <c r="P29">
-        <v>1.1344872752</v>
+        <v>1.1248756928</v>
       </c>
       <c r="Q29">
-        <v>1.2544872752</v>
+        <v>1.2448756928</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1405483885830682</v>
+        <v>0.1417141596776141</v>
       </c>
       <c r="T29">
-        <v>1.304247232611509</v>
+        <v>1.320294510529982</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.371605577623682</v>
+        <v>5.179762521279979</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1151955949678821</v>
+        <v>0.1150995162701245</v>
       </c>
       <c r="C30">
-        <v>15.22693582278316</v>
+        <v>15.03898332144992</v>
       </c>
       <c r="D30">
-        <v>14.73237582278316</v>
+        <v>14.74890332144992</v>
       </c>
       <c r="E30">
-        <v>5.077440000000001</v>
+        <v>5.281920000000001</v>
       </c>
       <c r="F30">
-        <v>5.725440000000001</v>
+        <v>5.929920000000001</v>
       </c>
       <c r="G30">
         <v>6.22</v>
@@ -3735,28 +3735,28 @@
         <v>1.64</v>
       </c>
       <c r="M30">
-        <v>0.3166168320000001</v>
+        <v>0.3279245760000001</v>
       </c>
       <c r="N30">
-        <v>1.323383168</v>
+        <v>1.312075424</v>
       </c>
       <c r="O30">
-        <v>0.1985074752</v>
+        <v>0.1968113136</v>
       </c>
       <c r="P30">
-        <v>1.1248756928</v>
+        <v>1.1152641104</v>
       </c>
       <c r="Q30">
-        <v>1.2448756928</v>
+        <v>1.2352641104</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1417141596776141</v>
+        <v>0.1429127693945415</v>
       </c>
       <c r="T30">
-        <v>1.320294510529982</v>
+        <v>1.336793824446159</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.179762521279979</v>
+        <v>5.001150020546187</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1150995162701245</v>
+        <v>0.1150034375723668</v>
       </c>
       <c r="C31">
-        <v>15.03898332144993</v>
+        <v>14.85106794447489</v>
       </c>
       <c r="D31">
-        <v>14.74890332144992</v>
+        <v>14.76546794447489</v>
       </c>
       <c r="E31">
-        <v>5.28192</v>
+        <v>5.486400000000001</v>
       </c>
       <c r="F31">
-        <v>5.92992</v>
+        <v>6.1344</v>
       </c>
       <c r="G31">
         <v>6.22</v>
@@ -3817,28 +3817,28 @@
         <v>1.64</v>
       </c>
       <c r="M31">
-        <v>0.327924576</v>
+        <v>0.33923232</v>
       </c>
       <c r="N31">
-        <v>1.312075424</v>
+        <v>1.30076768</v>
       </c>
       <c r="O31">
-        <v>0.1968113136</v>
+        <v>0.195115152</v>
       </c>
       <c r="P31">
-        <v>1.1152641104</v>
+        <v>1.105652528</v>
       </c>
       <c r="Q31">
-        <v>1.2352641104</v>
+        <v>1.225652528</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1429127693945415</v>
+        <v>0.1441456251033812</v>
       </c>
       <c r="T31">
-        <v>1.336793824446159</v>
+        <v>1.353764547331368</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.001150020546187</v>
+        <v>4.834445019861315</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1150034375723668</v>
+        <v>0.1149073588746092</v>
       </c>
       <c r="C32">
-        <v>14.85106794447489</v>
+        <v>14.66318981708278</v>
       </c>
       <c r="D32">
-        <v>14.76546794447489</v>
+        <v>14.78206981708278</v>
       </c>
       <c r="E32">
-        <v>5.486400000000001</v>
+        <v>5.690880000000001</v>
       </c>
       <c r="F32">
-        <v>6.1344</v>
+        <v>6.338880000000001</v>
       </c>
       <c r="G32">
         <v>6.22</v>
@@ -3899,28 +3899,28 @@
         <v>1.64</v>
       </c>
       <c r="M32">
-        <v>0.33923232</v>
+        <v>0.350540064</v>
       </c>
       <c r="N32">
-        <v>1.30076768</v>
+        <v>1.289459936</v>
       </c>
       <c r="O32">
-        <v>0.195115152</v>
+        <v>0.1934189904</v>
       </c>
       <c r="P32">
-        <v>1.105652528</v>
+        <v>1.0960409456</v>
       </c>
       <c r="Q32">
-        <v>1.225652528</v>
+        <v>1.2160409456</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1441456251033812</v>
+        <v>0.1454142157603032</v>
       </c>
       <c r="T32">
-        <v>1.353764547331368</v>
+        <v>1.371227175227744</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.834445019861315</v>
+        <v>4.678495180510949</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1149073588746092</v>
+        <v>0.1148112801768515</v>
       </c>
       <c r="C33">
-        <v>14.66318981708278</v>
+        <v>14.47534906506213</v>
       </c>
       <c r="D33">
-        <v>14.78206981708278</v>
+        <v>14.79870906506213</v>
       </c>
       <c r="E33">
-        <v>5.690880000000001</v>
+        <v>5.89536</v>
       </c>
       <c r="F33">
-        <v>6.338880000000001</v>
+        <v>6.54336</v>
       </c>
       <c r="G33">
         <v>6.22</v>
@@ -3981,28 +3981,28 @@
         <v>1.64</v>
       </c>
       <c r="M33">
-        <v>0.350540064</v>
+        <v>0.361847808</v>
       </c>
       <c r="N33">
-        <v>1.289459936</v>
+        <v>1.278152192</v>
       </c>
       <c r="O33">
-        <v>0.1934189904</v>
+        <v>0.1917228288</v>
       </c>
       <c r="P33">
-        <v>1.0960409456</v>
+        <v>1.0864293632</v>
       </c>
       <c r="Q33">
-        <v>1.2160409456</v>
+        <v>1.2064293632</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1454142157603032</v>
+        <v>0.1467201179071346</v>
       </c>
       <c r="T33">
-        <v>1.371227175227744</v>
+        <v>1.389203409826954</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.678495180510949</v>
+        <v>4.532292206119982</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1148112801768515</v>
+        <v>0.1154164514790939</v>
       </c>
       <c r="C34">
-        <v>14.47534906506213</v>
+        <v>14.1666840673025</v>
       </c>
       <c r="D34">
-        <v>14.79870906506213</v>
+        <v>14.6945240673025</v>
       </c>
       <c r="E34">
-        <v>5.89536</v>
+        <v>6.09984</v>
       </c>
       <c r="F34">
-        <v>6.54336</v>
+        <v>6.74784</v>
       </c>
       <c r="G34">
         <v>6.22</v>
@@ -4063,45 +4063,45 @@
         <v>1.64</v>
       </c>
       <c r="M34">
-        <v>0.361847808</v>
+        <v>0.390025152</v>
       </c>
       <c r="N34">
-        <v>1.278152192</v>
+        <v>1.249974848</v>
       </c>
       <c r="O34">
-        <v>0.1917228288</v>
+        <v>0.1874962272</v>
       </c>
       <c r="P34">
-        <v>1.0864293632</v>
+        <v>1.0624786208</v>
       </c>
       <c r="Q34">
-        <v>1.2064293632</v>
+        <v>1.1824786208</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1467201179071346</v>
+        <v>0.1480650022076028</v>
       </c>
       <c r="T34">
-        <v>1.389203409826954</v>
+        <v>1.407716248444051</v>
       </c>
       <c r="U34">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>4.532292206119982</v>
+        <v>4.204857024195197</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1154164514790939</v>
+        <v>0.1153416227813363</v>
       </c>
       <c r="C35">
-        <v>14.1666840673025</v>
+        <v>13.97500686730185</v>
       </c>
       <c r="D35">
-        <v>14.6945240673025</v>
+        <v>14.70732686730186</v>
       </c>
       <c r="E35">
-        <v>6.09984</v>
+        <v>6.304320000000001</v>
       </c>
       <c r="F35">
-        <v>6.74784</v>
+        <v>6.95232</v>
       </c>
       <c r="G35">
         <v>6.22</v>
@@ -4145,28 +4145,28 @@
         <v>1.64</v>
       </c>
       <c r="M35">
-        <v>0.390025152</v>
+        <v>0.401844096</v>
       </c>
       <c r="N35">
-        <v>1.249974848</v>
+        <v>1.238155904</v>
       </c>
       <c r="O35">
-        <v>0.1874962272</v>
+        <v>0.1857233856</v>
       </c>
       <c r="P35">
-        <v>1.0624786208</v>
+        <v>1.0524325184</v>
       </c>
       <c r="Q35">
-        <v>1.1824786208</v>
+        <v>1.1724325184</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1480650022076028</v>
+        <v>0.1494506405777822</v>
       </c>
       <c r="T35">
-        <v>1.407716248444051</v>
+        <v>1.426790082170757</v>
       </c>
       <c r="U35">
         <v>0.0578</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.204857024195197</v>
+        <v>4.081184758777692</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1153416227813363</v>
+        <v>0.1163080440835786</v>
       </c>
       <c r="C36">
-        <v>13.97500686730185</v>
+        <v>13.60687464987294</v>
       </c>
       <c r="D36">
-        <v>14.70732686730186</v>
+        <v>14.54367464987294</v>
       </c>
       <c r="E36">
-        <v>6.304320000000001</v>
+        <v>6.508800000000001</v>
       </c>
       <c r="F36">
-        <v>6.95232</v>
+        <v>7.1568</v>
       </c>
       <c r="G36">
         <v>6.22</v>
@@ -4227,45 +4227,45 @@
         <v>1.64</v>
       </c>
       <c r="M36">
-        <v>0.401844096</v>
+        <v>0.43871184</v>
       </c>
       <c r="N36">
-        <v>1.238155904</v>
+        <v>1.20128816</v>
       </c>
       <c r="O36">
-        <v>0.1857233856</v>
+        <v>0.180193224</v>
       </c>
       <c r="P36">
-        <v>1.0524325184</v>
+        <v>1.021094936</v>
       </c>
       <c r="Q36">
-        <v>1.1724325184</v>
+        <v>1.141094936</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1494506405777822</v>
+        <v>0.1508789139747364</v>
       </c>
       <c r="T36">
-        <v>1.426790082170757</v>
+        <v>1.446450803089054</v>
       </c>
       <c r="U36">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.081184758777692</v>
+        <v>3.738216866907444</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1163080440835786</v>
+        <v>0.116262965385821</v>
       </c>
       <c r="C37">
-        <v>13.60687464987294</v>
+        <v>13.4099471829873</v>
       </c>
       <c r="D37">
-        <v>14.54367464987294</v>
+        <v>14.5512271829873</v>
       </c>
       <c r="E37">
-        <v>6.508800000000001</v>
+        <v>6.713280000000001</v>
       </c>
       <c r="F37">
-        <v>7.1568</v>
+        <v>7.361280000000001</v>
       </c>
       <c r="G37">
         <v>6.22</v>
@@ -4309,28 +4309,28 @@
         <v>1.64</v>
       </c>
       <c r="M37">
-        <v>0.43871184</v>
+        <v>0.4512464640000001</v>
       </c>
       <c r="N37">
-        <v>1.20128816</v>
+        <v>1.188753536</v>
       </c>
       <c r="O37">
-        <v>0.180193224</v>
+        <v>0.1783130304</v>
       </c>
       <c r="P37">
-        <v>1.021094936</v>
+        <v>1.0104405056</v>
       </c>
       <c r="Q37">
-        <v>1.141094936</v>
+        <v>1.1304405056</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1508789139747364</v>
+        <v>0.1523518209153453</v>
       </c>
       <c r="T37">
-        <v>1.446450803089054</v>
+        <v>1.466725921536048</v>
       </c>
       <c r="U37">
         <v>0.0613</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.738216866907444</v>
+        <v>3.634377509493348</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.116262965385821</v>
+        <v>0.1162178866880633</v>
       </c>
       <c r="C38">
-        <v>13.4099471829873</v>
+        <v>13.21302756424108</v>
       </c>
       <c r="D38">
-        <v>14.5512271829873</v>
+        <v>14.55878756424108</v>
       </c>
       <c r="E38">
-        <v>6.71328</v>
+        <v>6.91776</v>
       </c>
       <c r="F38">
-        <v>7.36128</v>
+        <v>7.56576</v>
       </c>
       <c r="G38">
         <v>6.22</v>
@@ -4391,28 +4391,28 @@
         <v>1.64</v>
       </c>
       <c r="M38">
-        <v>0.451246464</v>
+        <v>0.463781088</v>
       </c>
       <c r="N38">
-        <v>1.188753536</v>
+        <v>1.176218912</v>
       </c>
       <c r="O38">
-        <v>0.1783130304</v>
+        <v>0.1764328368</v>
       </c>
       <c r="P38">
-        <v>1.0104405056</v>
+        <v>0.9997860752</v>
       </c>
       <c r="Q38">
-        <v>1.1304405056</v>
+        <v>1.1197860752</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1523518209153452</v>
+        <v>0.1538714868064497</v>
       </c>
       <c r="T38">
-        <v>1.466725921536047</v>
+        <v>1.487644694536914</v>
       </c>
       <c r="U38">
         <v>0.0613</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.634377509493348</v>
+        <v>3.536151090317853</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1162178866880633</v>
+        <v>0.1170772079903057</v>
       </c>
       <c r="C39">
-        <v>13.21302756424108</v>
+        <v>12.86576563847624</v>
       </c>
       <c r="D39">
-        <v>14.55878756424108</v>
+        <v>14.41600563847624</v>
       </c>
       <c r="E39">
-        <v>6.91776</v>
+        <v>7.122240000000001</v>
       </c>
       <c r="F39">
-        <v>7.56576</v>
+        <v>7.77024</v>
       </c>
       <c r="G39">
         <v>6.22</v>
@@ -4473,45 +4473,45 @@
         <v>1.64</v>
       </c>
       <c r="M39">
-        <v>0.463781088</v>
+        <v>0.498072384</v>
       </c>
       <c r="N39">
-        <v>1.176218912</v>
+        <v>1.141927616</v>
       </c>
       <c r="O39">
-        <v>0.1764328368</v>
+        <v>0.1712891424</v>
       </c>
       <c r="P39">
-        <v>0.9997860752</v>
+        <v>0.9706384735999999</v>
       </c>
       <c r="Q39">
-        <v>1.1197860752</v>
+        <v>1.0906384736</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1538714868064497</v>
+        <v>0.1554401741779124</v>
       </c>
       <c r="T39">
-        <v>1.487644694536914</v>
+        <v>1.50923826666684</v>
       </c>
       <c r="U39">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V39">
         <v>0.15</v>
       </c>
       <c r="W39">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y39">
-        <v>3.536151090317853</v>
+        <v>3.292694099659217</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1170772079903057</v>
+        <v>0.117055929292548</v>
       </c>
       <c r="C40">
-        <v>12.86576563847624</v>
+        <v>12.66478741090283</v>
       </c>
       <c r="D40">
-        <v>14.41600563847624</v>
+        <v>14.41950741090283</v>
       </c>
       <c r="E40">
-        <v>7.122240000000001</v>
+        <v>7.326720000000001</v>
       </c>
       <c r="F40">
-        <v>7.77024</v>
+        <v>7.97472</v>
       </c>
       <c r="G40">
         <v>6.22</v>
@@ -4555,28 +4555,28 @@
         <v>1.64</v>
       </c>
       <c r="M40">
-        <v>0.498072384</v>
+        <v>0.5111795520000001</v>
       </c>
       <c r="N40">
-        <v>1.141927616</v>
+        <v>1.128820448</v>
       </c>
       <c r="O40">
-        <v>0.1712891424</v>
+        <v>0.1693230672</v>
       </c>
       <c r="P40">
-        <v>0.9706384735999999</v>
+        <v>0.9594973807999999</v>
       </c>
       <c r="Q40">
-        <v>1.0906384736</v>
+        <v>1.0794973808</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1554401741779124</v>
+        <v>0.1570602939222099</v>
       </c>
       <c r="T40">
-        <v>1.50923826666684</v>
+        <v>1.53153982476824</v>
       </c>
       <c r="U40">
         <v>0.0641</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.292694099659217</v>
+        <v>3.208266045821801</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.117055929292548</v>
+        <v>0.1170346505947904</v>
       </c>
       <c r="C41">
-        <v>12.66478741090283</v>
+        <v>12.46381088496435</v>
       </c>
       <c r="D41">
-        <v>14.41950741090283</v>
+        <v>14.42301088496435</v>
       </c>
       <c r="E41">
-        <v>7.326720000000001</v>
+        <v>7.5312</v>
       </c>
       <c r="F41">
-        <v>7.97472</v>
+        <v>8.1792</v>
       </c>
       <c r="G41">
         <v>6.22</v>
@@ -4637,28 +4637,28 @@
         <v>1.64</v>
       </c>
       <c r="M41">
-        <v>0.5111795520000001</v>
+        <v>0.52428672</v>
       </c>
       <c r="N41">
-        <v>1.128820448</v>
+        <v>1.11571328</v>
       </c>
       <c r="O41">
-        <v>0.1693230672</v>
+        <v>0.167356992</v>
       </c>
       <c r="P41">
-        <v>0.9594973807999999</v>
+        <v>0.948356288</v>
       </c>
       <c r="Q41">
-        <v>1.0794973808</v>
+        <v>1.068356288</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1570602939222099</v>
+        <v>0.158734417657984</v>
       </c>
       <c r="T41">
-        <v>1.53153982476824</v>
+        <v>1.554584768139687</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.208266045821801</v>
+        <v>3.128059394676256</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1170346505947904</v>
+        <v>0.1170133718970327</v>
       </c>
       <c r="C42">
-        <v>12.46381088496435</v>
+        <v>12.26283606190147</v>
       </c>
       <c r="D42">
-        <v>14.42301088496435</v>
+        <v>14.42651606190147</v>
       </c>
       <c r="E42">
-        <v>7.5312</v>
+        <v>7.73568</v>
       </c>
       <c r="F42">
-        <v>8.1792</v>
+        <v>8.38368</v>
       </c>
       <c r="G42">
         <v>6.22</v>
@@ -4719,28 +4719,28 @@
         <v>1.64</v>
       </c>
       <c r="M42">
-        <v>0.52428672</v>
+        <v>0.537393888</v>
       </c>
       <c r="N42">
-        <v>1.11571328</v>
+        <v>1.102606112</v>
       </c>
       <c r="O42">
-        <v>0.167356992</v>
+        <v>0.1653909168</v>
       </c>
       <c r="P42">
-        <v>0.948356288</v>
+        <v>0.9372151952</v>
       </c>
       <c r="Q42">
-        <v>1.068356288</v>
+        <v>1.0572151952</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.158734417657984</v>
+        <v>0.160465291350903</v>
       </c>
       <c r="T42">
-        <v>1.554584768139687</v>
+        <v>1.578410896032199</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.128059394676256</v>
+        <v>3.051765263098787</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1170133718970327</v>
+        <v>0.1197766931992751</v>
       </c>
       <c r="C43">
-        <v>12.26283606190147</v>
+        <v>11.6169815801008</v>
       </c>
       <c r="D43">
-        <v>14.42651606190147</v>
+        <v>13.9851415801008</v>
       </c>
       <c r="E43">
-        <v>7.73568</v>
+        <v>7.940160000000001</v>
       </c>
       <c r="F43">
-        <v>8.38368</v>
+        <v>8.58816</v>
       </c>
       <c r="G43">
         <v>6.22</v>
@@ -4801,45 +4801,45 @@
         <v>1.64</v>
       </c>
       <c r="M43">
-        <v>0.537393888</v>
+        <v>0.6174887040000001</v>
       </c>
       <c r="N43">
-        <v>1.102606112</v>
+        <v>1.022511296</v>
       </c>
       <c r="O43">
-        <v>0.1653909168</v>
+        <v>0.1533766944</v>
       </c>
       <c r="P43">
-        <v>0.9372151952</v>
+        <v>0.8691346015999999</v>
       </c>
       <c r="Q43">
-        <v>1.0572151952</v>
+        <v>0.9891346016</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.160465291350903</v>
+        <v>0.1622558503435778</v>
       </c>
       <c r="T43">
-        <v>1.578410896032199</v>
+        <v>1.603058614541695</v>
       </c>
       <c r="U43">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V43">
         <v>0.15</v>
       </c>
       <c r="W43">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.051765263098787</v>
+        <v>2.65591903038278</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1197766931992751</v>
+        <v>0.1198217145015175</v>
       </c>
       <c r="C44">
-        <v>11.61698158010079</v>
+        <v>11.40553398561585</v>
       </c>
       <c r="D44">
-        <v>13.98514158010079</v>
+        <v>13.97817398561585</v>
       </c>
       <c r="E44">
-        <v>7.940160000000001</v>
+        <v>8.144640000000001</v>
       </c>
       <c r="F44">
-        <v>8.58816</v>
+        <v>8.79264</v>
       </c>
       <c r="G44">
         <v>6.22</v>
@@ -4883,28 +4883,28 @@
         <v>1.64</v>
       </c>
       <c r="M44">
-        <v>0.6174887040000001</v>
+        <v>0.632190816</v>
       </c>
       <c r="N44">
-        <v>1.022511296</v>
+        <v>1.007809184</v>
       </c>
       <c r="O44">
-        <v>0.1533766944</v>
+        <v>0.1511713776</v>
       </c>
       <c r="P44">
-        <v>0.8691346015999999</v>
+        <v>0.8566378063999999</v>
       </c>
       <c r="Q44">
-        <v>0.9891346016</v>
+        <v>0.9766378064</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1622558503435778</v>
+        <v>0.1641092359675745</v>
       </c>
       <c r="T44">
-        <v>1.603058614541694</v>
+        <v>1.628571165279593</v>
       </c>
       <c r="U44">
         <v>0.07190000000000001</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.65591903038278</v>
+        <v>2.59415347153667</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1198217145015175</v>
+        <v>0.1198667358037598</v>
       </c>
       <c r="C45">
-        <v>11.40553398561585</v>
+        <v>11.19409333038105</v>
       </c>
       <c r="D45">
-        <v>13.97817398561585</v>
+        <v>13.97121333038105</v>
       </c>
       <c r="E45">
-        <v>8.144640000000001</v>
+        <v>8.349120000000001</v>
       </c>
       <c r="F45">
-        <v>8.79264</v>
+        <v>8.997120000000001</v>
       </c>
       <c r="G45">
         <v>6.22</v>
@@ -4965,28 +4965,28 @@
         <v>1.64</v>
       </c>
       <c r="M45">
-        <v>0.632190816</v>
+        <v>0.6468929280000001</v>
       </c>
       <c r="N45">
-        <v>1.007809184</v>
+        <v>0.9931070719999998</v>
       </c>
       <c r="O45">
-        <v>0.1511713776</v>
+        <v>0.1489660608</v>
       </c>
       <c r="P45">
-        <v>0.8566378063999999</v>
+        <v>0.8441410111999998</v>
       </c>
       <c r="Q45">
-        <v>0.9766378064</v>
+        <v>0.9641410112</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1641092359675745</v>
+        <v>0.1660288139352854</v>
       </c>
       <c r="T45">
-        <v>1.628571165279593</v>
+        <v>1.654994878543846</v>
       </c>
       <c r="U45">
         <v>0.07190000000000001</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.59415347153667</v>
+        <v>2.535195438092654</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1198667358037598</v>
+        <v>0.1214035071060022</v>
       </c>
       <c r="C46">
-        <v>11.19409333038105</v>
+        <v>10.75610358400368</v>
       </c>
       <c r="D46">
-        <v>13.97121333038105</v>
+        <v>13.73770358400368</v>
       </c>
       <c r="E46">
-        <v>8.349120000000001</v>
+        <v>8.553600000000001</v>
       </c>
       <c r="F46">
-        <v>8.997120000000001</v>
+        <v>9.201600000000001</v>
       </c>
       <c r="G46">
         <v>6.22</v>
@@ -5047,45 +5047,45 @@
         <v>1.64</v>
       </c>
       <c r="M46">
-        <v>0.6468929280000001</v>
+        <v>0.6974812800000001</v>
       </c>
       <c r="N46">
-        <v>0.9931070719999998</v>
+        <v>0.9425187199999998</v>
       </c>
       <c r="O46">
-        <v>0.1489660608</v>
+        <v>0.141377808</v>
       </c>
       <c r="P46">
-        <v>0.8441410111999998</v>
+        <v>0.8011409119999998</v>
       </c>
       <c r="Q46">
-        <v>0.9641410112</v>
+        <v>0.9211409119999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1660288139352854</v>
+        <v>0.1680181947381857</v>
       </c>
       <c r="T46">
-        <v>1.654994878543846</v>
+        <v>1.682379454108616</v>
       </c>
       <c r="U46">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.535195438092654</v>
+        <v>2.351317586616805</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1214035071060022</v>
+        <v>0.1214816784082445</v>
       </c>
       <c r="C47">
-        <v>10.75610358400368</v>
+        <v>10.53995403520411</v>
       </c>
       <c r="D47">
-        <v>13.73770358400368</v>
+        <v>13.72603403520411</v>
       </c>
       <c r="E47">
-        <v>8.553600000000001</v>
+        <v>8.758080000000001</v>
       </c>
       <c r="F47">
-        <v>9.201600000000001</v>
+        <v>9.406080000000001</v>
       </c>
       <c r="G47">
         <v>6.22</v>
@@ -5129,28 +5129,28 @@
         <v>1.64</v>
       </c>
       <c r="M47">
-        <v>0.6974812800000001</v>
+        <v>0.7129808640000002</v>
       </c>
       <c r="N47">
-        <v>0.9425187199999998</v>
+        <v>0.9270191359999997</v>
       </c>
       <c r="O47">
-        <v>0.141377808</v>
+        <v>0.1390528703999999</v>
       </c>
       <c r="P47">
-        <v>0.8011409119999998</v>
+        <v>0.7879662655999998</v>
       </c>
       <c r="Q47">
-        <v>0.9211409119999999</v>
+        <v>0.9079662655999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1680181947381857</v>
+        <v>0.1700812563115639</v>
       </c>
       <c r="T47">
-        <v>1.682379454108616</v>
+        <v>1.710778273212823</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.351317586616805</v>
+        <v>2.300201986907743</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1214816784082445</v>
+        <v>0.1215598497104869</v>
       </c>
       <c r="C48">
-        <v>10.53995403520411</v>
+        <v>10.32382429507041</v>
       </c>
       <c r="D48">
-        <v>13.72603403520411</v>
+        <v>13.71438429507041</v>
       </c>
       <c r="E48">
-        <v>8.758080000000001</v>
+        <v>8.962560000000002</v>
       </c>
       <c r="F48">
-        <v>9.406080000000001</v>
+        <v>9.610560000000001</v>
       </c>
       <c r="G48">
         <v>6.22</v>
@@ -5211,28 +5211,28 @@
         <v>1.64</v>
       </c>
       <c r="M48">
-        <v>0.7129808640000002</v>
+        <v>0.7284804480000001</v>
       </c>
       <c r="N48">
-        <v>0.9270191359999997</v>
+        <v>0.9115195519999998</v>
       </c>
       <c r="O48">
-        <v>0.1390528703999999</v>
+        <v>0.1367279328</v>
       </c>
       <c r="P48">
-        <v>0.7879662655999998</v>
+        <v>0.7747916191999998</v>
       </c>
       <c r="Q48">
-        <v>0.9079662655999999</v>
+        <v>0.8947916191999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1700812563115639</v>
+        <v>0.1722221692650696</v>
       </c>
       <c r="T48">
-        <v>1.710778273212823</v>
+        <v>1.740248745868132</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.300201986907743</v>
+        <v>2.251261519101196</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1215598497104869</v>
+        <v>0.1216380210127292</v>
       </c>
       <c r="C49">
-        <v>10.32382429507041</v>
+        <v>10.10771431320854</v>
       </c>
       <c r="D49">
-        <v>13.71438429507041</v>
+        <v>13.70275431320855</v>
       </c>
       <c r="E49">
-        <v>8.962560000000002</v>
+        <v>9.167040000000002</v>
       </c>
       <c r="F49">
-        <v>9.610560000000001</v>
+        <v>9.815040000000002</v>
       </c>
       <c r="G49">
         <v>6.22</v>
@@ -5293,28 +5293,28 @@
         <v>1.64</v>
       </c>
       <c r="M49">
-        <v>0.7284804480000001</v>
+        <v>0.7439800320000002</v>
       </c>
       <c r="N49">
-        <v>0.9115195519999998</v>
+        <v>0.8960199679999997</v>
       </c>
       <c r="O49">
-        <v>0.1367279328</v>
+        <v>0.1344029952</v>
       </c>
       <c r="P49">
-        <v>0.7747916191999998</v>
+        <v>0.7616169727999997</v>
       </c>
       <c r="Q49">
-        <v>0.8947916191999999</v>
+        <v>0.8816169727999998</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1722221692650696</v>
+        <v>0.1744454250244793</v>
       </c>
       <c r="T49">
-        <v>1.740248745868132</v>
+        <v>1.770852698240952</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.251261519101196</v>
+        <v>2.204360237453254</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1216380210127292</v>
+        <v>0.1217161923149716</v>
       </c>
       <c r="C50">
-        <v>10.10771431320855</v>
+        <v>9.891624039395268</v>
       </c>
       <c r="D50">
-        <v>13.70275431320855</v>
+        <v>13.69114403939527</v>
       </c>
       <c r="E50">
-        <v>9.16704</v>
+        <v>9.37152</v>
       </c>
       <c r="F50">
-        <v>9.81504</v>
+        <v>10.01952</v>
       </c>
       <c r="G50">
         <v>6.22</v>
@@ -5375,28 +5375,28 @@
         <v>1.64</v>
       </c>
       <c r="M50">
-        <v>0.7439800320000001</v>
+        <v>0.759479616</v>
       </c>
       <c r="N50">
-        <v>0.8960199679999998</v>
+        <v>0.8805203839999999</v>
       </c>
       <c r="O50">
-        <v>0.1344029952</v>
+        <v>0.1320780576</v>
       </c>
       <c r="P50">
-        <v>0.7616169727999998</v>
+        <v>0.7484423264</v>
       </c>
       <c r="Q50">
-        <v>0.8816169728</v>
+        <v>0.8684423264000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1744454250244793</v>
+        <v>0.176755867284258</v>
       </c>
       <c r="T50">
-        <v>1.770852698240952</v>
+        <v>1.802656805608785</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.204360237453254</v>
+        <v>2.159373293831759</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1217161923149716</v>
+        <v>0.121794363617214</v>
       </c>
       <c r="C51">
-        <v>9.891624039395268</v>
+        <v>9.675553423577384</v>
       </c>
       <c r="D51">
-        <v>13.69114403939527</v>
+        <v>13.67955342357738</v>
       </c>
       <c r="E51">
-        <v>9.37152</v>
+        <v>9.576000000000001</v>
       </c>
       <c r="F51">
-        <v>10.01952</v>
+        <v>10.224</v>
       </c>
       <c r="G51">
         <v>6.22</v>
@@ -5457,28 +5457,28 @@
         <v>1.64</v>
       </c>
       <c r="M51">
-        <v>0.759479616</v>
+        <v>0.7749792000000001</v>
       </c>
       <c r="N51">
-        <v>0.8805203839999999</v>
+        <v>0.8650207999999998</v>
       </c>
       <c r="O51">
-        <v>0.1320780576</v>
+        <v>0.12975312</v>
       </c>
       <c r="P51">
-        <v>0.7484423264</v>
+        <v>0.7352676799999999</v>
       </c>
       <c r="Q51">
-        <v>0.8684423264000001</v>
+        <v>0.85526768</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.176755867284258</v>
+        <v>0.1791587272344279</v>
       </c>
       <c r="T51">
-        <v>1.802656805608785</v>
+        <v>1.835733077271332</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.159373293831759</v>
+        <v>2.116185827955124</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.121794363617214</v>
+        <v>0.1218725349194563</v>
       </c>
       <c r="C52">
-        <v>9.675553423577384</v>
+        <v>9.459502415871089</v>
       </c>
       <c r="D52">
-        <v>13.67955342357738</v>
+        <v>13.66798241587109</v>
       </c>
       <c r="E52">
-        <v>9.576000000000001</v>
+        <v>9.780480000000001</v>
       </c>
       <c r="F52">
-        <v>10.224</v>
+        <v>10.42848</v>
       </c>
       <c r="G52">
         <v>6.22</v>
@@ -5539,28 +5539,28 @@
         <v>1.64</v>
       </c>
       <c r="M52">
-        <v>0.7749792000000001</v>
+        <v>0.790478784</v>
       </c>
       <c r="N52">
-        <v>0.8650207999999998</v>
+        <v>0.8495212159999999</v>
       </c>
       <c r="O52">
-        <v>0.12975312</v>
+        <v>0.1274281824</v>
       </c>
       <c r="P52">
-        <v>0.7352676799999999</v>
+        <v>0.7220930335999999</v>
       </c>
       <c r="Q52">
-        <v>0.85526768</v>
+        <v>0.8420930336</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1791587272344279</v>
+        <v>0.1816596631009312</v>
       </c>
       <c r="T52">
-        <v>1.835733077271332</v>
+        <v>1.870159400838472</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.116185827955124</v>
+        <v>2.074691988191298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1218725349194563</v>
+        <v>0.1219507062216987</v>
       </c>
       <c r="C53">
-        <v>9.459502415871089</v>
+        <v>9.24347096656118</v>
       </c>
       <c r="D53">
-        <v>13.66798241587109</v>
+        <v>13.65643096656118</v>
       </c>
       <c r="E53">
-        <v>9.780480000000001</v>
+        <v>9.984960000000001</v>
       </c>
       <c r="F53">
-        <v>10.42848</v>
+        <v>10.63296</v>
       </c>
       <c r="G53">
         <v>6.22</v>
@@ -5621,28 +5621,28 @@
         <v>1.64</v>
       </c>
       <c r="M53">
-        <v>0.790478784</v>
+        <v>0.8059783680000001</v>
       </c>
       <c r="N53">
-        <v>0.8495212159999999</v>
+        <v>0.8340216319999998</v>
       </c>
       <c r="O53">
-        <v>0.1274281824</v>
+        <v>0.1251032448</v>
       </c>
       <c r="P53">
-        <v>0.7220930335999999</v>
+        <v>0.7089183871999998</v>
       </c>
       <c r="Q53">
-        <v>0.8420930336</v>
+        <v>0.8289183871999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1816596631009312</v>
+        <v>0.1842648046285389</v>
       </c>
       <c r="T53">
-        <v>1.870159400838472</v>
+        <v>1.906020154554243</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.074691988191298</v>
+        <v>2.034794065341465</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1219507062216987</v>
+        <v>0.128425977523941</v>
       </c>
       <c r="C54">
-        <v>9.24347096656118</v>
+        <v>8.145493752501817</v>
       </c>
       <c r="D54">
-        <v>13.65643096656118</v>
+        <v>12.76293375250182</v>
       </c>
       <c r="E54">
-        <v>9.984960000000001</v>
+        <v>10.18944</v>
       </c>
       <c r="F54">
-        <v>10.63296</v>
+        <v>10.83744</v>
       </c>
       <c r="G54">
         <v>6.22</v>
@@ -5703,45 +5703,45 @@
         <v>1.64</v>
       </c>
       <c r="M54">
-        <v>0.8059783680000001</v>
+        <v>0.9753696000000001</v>
       </c>
       <c r="N54">
-        <v>0.8340216319999998</v>
+        <v>0.6646303999999998</v>
       </c>
       <c r="O54">
-        <v>0.1251032448</v>
+        <v>0.09969455999999997</v>
       </c>
       <c r="P54">
-        <v>0.7089183871999998</v>
+        <v>0.5649358399999999</v>
       </c>
       <c r="Q54">
-        <v>0.8289183871999999</v>
+        <v>0.68493584</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1842648046285389</v>
+        <v>0.1869808032424277</v>
       </c>
       <c r="T54">
-        <v>1.906020154554243</v>
+        <v>1.943406897789834</v>
       </c>
       <c r="U54">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V54">
         <v>0.15</v>
       </c>
       <c r="W54">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.034794065341465</v>
+        <v>1.681413896844847</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.128425977523941</v>
+        <v>0.1286248488261834</v>
       </c>
       <c r="C55">
-        <v>8.145493752501817</v>
+        <v>7.915419122893454</v>
       </c>
       <c r="D55">
-        <v>12.76293375250182</v>
+        <v>12.73733912289345</v>
       </c>
       <c r="E55">
-        <v>10.18944</v>
+        <v>10.39392</v>
       </c>
       <c r="F55">
-        <v>10.83744</v>
+        <v>11.04192</v>
       </c>
       <c r="G55">
         <v>6.22</v>
@@ -5785,28 +5785,28 @@
         <v>1.64</v>
       </c>
       <c r="M55">
-        <v>0.9753696000000001</v>
+        <v>0.9937728</v>
       </c>
       <c r="N55">
-        <v>0.6646303999999998</v>
+        <v>0.6462271999999999</v>
       </c>
       <c r="O55">
-        <v>0.09969455999999997</v>
+        <v>0.09693407999999998</v>
       </c>
       <c r="P55">
-        <v>0.5649358399999999</v>
+        <v>0.54929312</v>
       </c>
       <c r="Q55">
-        <v>0.68493584</v>
+        <v>0.6692931200000001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1869808032424277</v>
+        <v>0.1898148887525725</v>
       </c>
       <c r="T55">
-        <v>1.943406897789834</v>
+        <v>1.982419151600886</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.681413896844847</v>
+        <v>1.650276602458832</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1286248488261834</v>
+        <v>0.1288237201284257</v>
       </c>
       <c r="C56">
-        <v>7.915419122893454</v>
+        <v>7.685446942143187</v>
       </c>
       <c r="D56">
-        <v>12.73733912289345</v>
+        <v>12.71184694214319</v>
       </c>
       <c r="E56">
-        <v>10.39392</v>
+        <v>10.5984</v>
       </c>
       <c r="F56">
-        <v>11.04192</v>
+        <v>11.2464</v>
       </c>
       <c r="G56">
         <v>6.22</v>
@@ -5867,28 +5867,28 @@
         <v>1.64</v>
       </c>
       <c r="M56">
-        <v>0.9937728</v>
+        <v>1.012176</v>
       </c>
       <c r="N56">
-        <v>0.6462271999999999</v>
+        <v>0.6278239999999997</v>
       </c>
       <c r="O56">
-        <v>0.09693407999999998</v>
+        <v>0.09417359999999995</v>
       </c>
       <c r="P56">
-        <v>0.54929312</v>
+        <v>0.5336503999999997</v>
       </c>
       <c r="Q56">
-        <v>0.6692931200000001</v>
+        <v>0.6536503999999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1898148887525725</v>
+        <v>0.1927749336187239</v>
       </c>
       <c r="T56">
-        <v>1.982419151600886</v>
+        <v>2.023165283359096</v>
       </c>
       <c r="U56">
         <v>0.09</v>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>1.650276602458832</v>
+        <v>1.620271573323216</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1288237201284257</v>
+        <v>0.1290225914306681</v>
       </c>
       <c r="C57">
-        <v>7.685446942143187</v>
+        <v>7.455576596364171</v>
       </c>
       <c r="D57">
-        <v>12.71184694214319</v>
+        <v>12.68645659636417</v>
       </c>
       <c r="E57">
-        <v>10.5984</v>
+        <v>10.80288</v>
       </c>
       <c r="F57">
-        <v>11.2464</v>
+        <v>11.45088</v>
       </c>
       <c r="G57">
         <v>6.22</v>
@@ -5949,28 +5949,28 @@
         <v>1.64</v>
       </c>
       <c r="M57">
-        <v>1.012176</v>
+        <v>1.0305792</v>
       </c>
       <c r="N57">
-        <v>0.6278239999999997</v>
+        <v>0.6094207999999999</v>
       </c>
       <c r="O57">
-        <v>0.09417359999999995</v>
+        <v>0.09141311999999997</v>
       </c>
       <c r="P57">
-        <v>0.5336503999999997</v>
+        <v>0.5180076799999999</v>
       </c>
       <c r="Q57">
-        <v>0.6536503999999999</v>
+        <v>0.63800768</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1927749336187239</v>
+        <v>0.1958695259787911</v>
       </c>
       <c r="T57">
-        <v>2.023165283359096</v>
+        <v>2.065763512015406</v>
       </c>
       <c r="U57">
         <v>0.09</v>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>1.620271573323216</v>
+        <v>1.591338152371016</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1290225914306681</v>
+        <v>0.1292214627329104</v>
       </c>
       <c r="C58">
-        <v>7.455576596364171</v>
+        <v>7.225807476564412</v>
       </c>
       <c r="D58">
-        <v>12.68645659636417</v>
+        <v>12.66116747656442</v>
       </c>
       <c r="E58">
-        <v>10.80288</v>
+        <v>11.00736</v>
       </c>
       <c r="F58">
-        <v>11.45088</v>
+        <v>11.65536</v>
       </c>
       <c r="G58">
         <v>6.22</v>
@@ -6031,28 +6031,28 @@
         <v>1.64</v>
       </c>
       <c r="M58">
-        <v>1.0305792</v>
+        <v>1.0489824</v>
       </c>
       <c r="N58">
-        <v>0.6094207999999999</v>
+        <v>0.5910175999999998</v>
       </c>
       <c r="O58">
-        <v>0.09141311999999997</v>
+        <v>0.08865263999999996</v>
       </c>
       <c r="P58">
-        <v>0.5180076799999999</v>
+        <v>0.5023649599999999</v>
       </c>
       <c r="Q58">
-        <v>0.63800768</v>
+        <v>0.62236496</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1958695259787911</v>
+        <v>0.1991080528672336</v>
       </c>
       <c r="T58">
-        <v>2.065763512015406</v>
+        <v>2.110343053632474</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.591338152371016</v>
+        <v>1.563419939171524</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1292214627329104</v>
+        <v>0.1294203340351528</v>
       </c>
       <c r="C59">
-        <v>7.225807476564412</v>
+        <v>6.996138978598118</v>
       </c>
       <c r="D59">
-        <v>12.66116747656442</v>
+        <v>12.63597897859812</v>
       </c>
       <c r="E59">
-        <v>11.00736</v>
+        <v>11.21184</v>
       </c>
       <c r="F59">
-        <v>11.65536</v>
+        <v>11.85984</v>
       </c>
       <c r="G59">
         <v>6.22</v>
@@ -6113,28 +6113,28 @@
         <v>1.64</v>
       </c>
       <c r="M59">
-        <v>1.0489824</v>
+        <v>1.0673856</v>
       </c>
       <c r="N59">
-        <v>0.5910175999999998</v>
+        <v>0.5726143999999997</v>
       </c>
       <c r="O59">
-        <v>0.08865263999999996</v>
+        <v>0.08589215999999995</v>
       </c>
       <c r="P59">
-        <v>0.5023649599999999</v>
+        <v>0.4867222399999998</v>
       </c>
       <c r="Q59">
-        <v>0.62236496</v>
+        <v>0.6067222399999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1991080528672336</v>
+        <v>0.2025007953217924</v>
       </c>
       <c r="T59">
-        <v>2.110343053632474</v>
+        <v>2.157045430564641</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.563419939171524</v>
+        <v>1.536464422978912</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1294203340351528</v>
+        <v>0.1296192053373951</v>
       </c>
       <c r="C60">
-        <v>6.99613897859812</v>
+        <v>6.766570503117576</v>
       </c>
       <c r="D60">
-        <v>12.63597897859812</v>
+        <v>12.61089050311758</v>
       </c>
       <c r="E60">
-        <v>11.21184</v>
+        <v>11.41632</v>
       </c>
       <c r="F60">
-        <v>11.85984</v>
+        <v>12.06432</v>
       </c>
       <c r="G60">
         <v>6.22</v>
@@ -6195,28 +6195,28 @@
         <v>1.64</v>
       </c>
       <c r="M60">
-        <v>1.0673856</v>
+        <v>1.0857888</v>
       </c>
       <c r="N60">
-        <v>0.5726144</v>
+        <v>0.5542111999999999</v>
       </c>
       <c r="O60">
-        <v>0.08589216</v>
+        <v>0.08313167999999999</v>
       </c>
       <c r="P60">
-        <v>0.48672224</v>
+        <v>0.4710795199999999</v>
       </c>
       <c r="Q60">
-        <v>0.6067222400000001</v>
+        <v>0.5910795200000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2025007953217924</v>
+        <v>0.2060590374082808</v>
       </c>
       <c r="T60">
-        <v>2.157045430564641</v>
+        <v>2.206025972225206</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.536464422978912</v>
+        <v>1.510422653097914</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1296192053373951</v>
+        <v>0.1605477249653785</v>
       </c>
       <c r="C61">
-        <v>6.766570503117576</v>
+        <v>3.586790683532064</v>
       </c>
       <c r="D61">
-        <v>12.61089050311758</v>
+        <v>9.635590683532063</v>
       </c>
       <c r="E61">
-        <v>11.41632</v>
+        <v>11.6208</v>
       </c>
       <c r="F61">
-        <v>12.06432</v>
+        <v>12.2688</v>
       </c>
       <c r="G61">
         <v>6.22</v>
@@ -6277,45 +6277,45 @@
         <v>1.64</v>
       </c>
       <c r="M61">
-        <v>1.0857888</v>
+        <v>1.80105984</v>
       </c>
       <c r="N61">
-        <v>0.5542111999999999</v>
+        <v>-0.1610598400000003</v>
       </c>
       <c r="O61">
-        <v>0.08313167999999999</v>
+        <v>-0.02415897600000004</v>
       </c>
       <c r="P61">
-        <v>0.4710795199999999</v>
+        <v>-0.1369008640000002</v>
       </c>
       <c r="Q61">
-        <v>0.5910795200000001</v>
+        <v>-0.01690086400000013</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2060590374082808</v>
+        <v>0.2112456034932584</v>
       </c>
       <c r="T61">
-        <v>2.206025972225206</v>
+        <v>2.27742100663424</v>
       </c>
       <c r="U61">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.15</v>
+        <v>0.1365862446857956</v>
       </c>
       <c r="W61">
-        <v>0.0765</v>
+        <v>0.1267491392801252</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.510422653097914</v>
+        <v>0.910574964571971</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1605477249653785</v>
+        <v>0.1615577249653785</v>
       </c>
       <c r="C62">
-        <v>3.586790683532064</v>
+        <v>3.308640399283076</v>
       </c>
       <c r="D62">
-        <v>9.635590683532063</v>
+        <v>9.561920399283078</v>
       </c>
       <c r="E62">
-        <v>11.6208</v>
+        <v>11.82528</v>
       </c>
       <c r="F62">
-        <v>12.2688</v>
+        <v>12.47328</v>
       </c>
       <c r="G62">
         <v>6.22</v>
@@ -6359,37 +6359,37 @@
         <v>1.64</v>
       </c>
       <c r="M62">
-        <v>1.80105984</v>
+        <v>1.831077504</v>
       </c>
       <c r="N62">
-        <v>-0.1610598400000003</v>
+        <v>-0.1910775040000003</v>
       </c>
       <c r="O62">
-        <v>-0.02415897600000004</v>
+        <v>-0.02866162560000005</v>
       </c>
       <c r="P62">
-        <v>-0.1369008640000002</v>
+        <v>-0.1624158784000003</v>
       </c>
       <c r="Q62">
-        <v>-0.01690086400000013</v>
+        <v>-0.04241587840000019</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2112456034932584</v>
+        <v>0.215487798454624</v>
       </c>
       <c r="T62">
-        <v>2.27742100663424</v>
+        <v>2.335816417060759</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1365862446857956</v>
+        <v>0.1343471259204547</v>
       </c>
       <c r="W62">
-        <v>0.1267491392801252</v>
+        <v>0.1270778419148773</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.910574964571971</v>
+        <v>0.8956475061363649</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1615577249653785</v>
+        <v>0.1625677249653785</v>
       </c>
       <c r="C63">
-        <v>3.308640399283076</v>
+        <v>3.031608080819405</v>
       </c>
       <c r="D63">
-        <v>9.561920399283078</v>
+        <v>9.489368080819407</v>
       </c>
       <c r="E63">
-        <v>11.82528</v>
+        <v>12.02976</v>
       </c>
       <c r="F63">
-        <v>12.47328</v>
+        <v>12.67776</v>
       </c>
       <c r="G63">
         <v>6.22</v>
@@ -6441,37 +6441,37 @@
         <v>1.64</v>
       </c>
       <c r="M63">
-        <v>1.831077504</v>
+        <v>1.861095168</v>
       </c>
       <c r="N63">
-        <v>-0.1910775040000003</v>
+        <v>-0.2210951680000004</v>
       </c>
       <c r="O63">
-        <v>-0.02866162560000005</v>
+        <v>-0.03316427520000006</v>
       </c>
       <c r="P63">
-        <v>-0.1624158784000003</v>
+        <v>-0.1879308928000003</v>
       </c>
       <c r="Q63">
-        <v>-0.04241587840000019</v>
+        <v>-0.06793089280000023</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.215487798454624</v>
+        <v>0.2199532668350088</v>
       </c>
       <c r="T63">
-        <v>2.335816417060759</v>
+        <v>2.397285270141305</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1343471259204547</v>
+        <v>0.1321802367927055</v>
       </c>
       <c r="W63">
-        <v>0.1270778419148773</v>
+        <v>0.1273959412388309</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8956475061363649</v>
+        <v>0.8812015786180364</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1625677249653785</v>
+        <v>0.1635777249653785</v>
       </c>
       <c r="C64">
-        <v>3.031608080819405</v>
+        <v>2.755668471644281</v>
       </c>
       <c r="D64">
-        <v>9.489368080819407</v>
+        <v>9.417908471644282</v>
       </c>
       <c r="E64">
-        <v>12.02976</v>
+        <v>12.23424</v>
       </c>
       <c r="F64">
-        <v>12.67776</v>
+        <v>12.88224</v>
       </c>
       <c r="G64">
         <v>6.22</v>
@@ -6523,37 +6523,37 @@
         <v>1.64</v>
       </c>
       <c r="M64">
-        <v>1.861095168</v>
+        <v>1.891112832</v>
       </c>
       <c r="N64">
-        <v>-0.2210951680000004</v>
+        <v>-0.2511128320000002</v>
       </c>
       <c r="O64">
-        <v>-0.03316427520000006</v>
+        <v>-0.03766692480000004</v>
       </c>
       <c r="P64">
-        <v>-0.1879308928000003</v>
+        <v>-0.2134459072000002</v>
       </c>
       <c r="Q64">
-        <v>-0.06793089280000023</v>
+        <v>-0.09344590720000009</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2199532668350088</v>
+        <v>0.2246601118846036</v>
       </c>
       <c r="T64">
-        <v>2.397285270141305</v>
+        <v>2.462076763928908</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.1321802367927055</v>
+        <v>0.1300821377959958</v>
       </c>
       <c r="W64">
-        <v>0.1273959412388309</v>
+        <v>0.1277039421715478</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.8812015786180364</v>
+        <v>0.8672142519733057</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1635777249653785</v>
+        <v>0.1645877249653785</v>
       </c>
       <c r="C65">
-        <v>2.755668471644281</v>
+        <v>2.480797070350111</v>
       </c>
       <c r="D65">
-        <v>9.417908471644282</v>
+        <v>9.34751707035011</v>
       </c>
       <c r="E65">
-        <v>12.23424</v>
+        <v>12.43872</v>
       </c>
       <c r="F65">
-        <v>12.88224</v>
+        <v>13.08672</v>
       </c>
       <c r="G65">
         <v>6.22</v>
@@ -6605,37 +6605,37 @@
         <v>1.64</v>
       </c>
       <c r="M65">
-        <v>1.891112832</v>
+        <v>1.921130496</v>
       </c>
       <c r="N65">
-        <v>-0.2511128320000002</v>
+        <v>-0.2811304960000003</v>
       </c>
       <c r="O65">
-        <v>-0.03766692480000004</v>
+        <v>-0.04216957440000004</v>
       </c>
       <c r="P65">
-        <v>-0.2134459072000002</v>
+        <v>-0.2389609216000002</v>
       </c>
       <c r="Q65">
-        <v>-0.09344590720000009</v>
+        <v>-0.1189609216000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2246601118846036</v>
+        <v>0.2296284483258426</v>
       </c>
       <c r="T65">
-        <v>2.462076763928908</v>
+        <v>2.530467785149155</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.1300821377959958</v>
+        <v>0.1280496043929334</v>
       </c>
       <c r="W65">
-        <v>0.1277039421715478</v>
+        <v>0.1280023180751174</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.8672142519733057</v>
+        <v>0.8536640292862228</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1645877249653785</v>
+        <v>0.1655977249653785</v>
       </c>
       <c r="C66">
-        <v>2.480797070350111</v>
+        <v>2.206970102609368</v>
       </c>
       <c r="D66">
-        <v>9.34751707035011</v>
+        <v>9.278170102609369</v>
       </c>
       <c r="E66">
-        <v>12.43872</v>
+        <v>12.6432</v>
       </c>
       <c r="F66">
-        <v>13.08672</v>
+        <v>13.2912</v>
       </c>
       <c r="G66">
         <v>6.22</v>
@@ -6687,37 +6687,37 @@
         <v>1.64</v>
       </c>
       <c r="M66">
-        <v>1.921130496</v>
+        <v>1.95114816</v>
       </c>
       <c r="N66">
-        <v>-0.2811304960000003</v>
+        <v>-0.3111481600000003</v>
       </c>
       <c r="O66">
-        <v>-0.04216957440000004</v>
+        <v>-0.04667222400000005</v>
       </c>
       <c r="P66">
-        <v>-0.2389609216000002</v>
+        <v>-0.2644759360000003</v>
       </c>
       <c r="Q66">
-        <v>-0.1189609216000001</v>
+        <v>-0.1444759360000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2296284483258426</v>
+        <v>0.234880689706581</v>
       </c>
       <c r="T66">
-        <v>2.530467785149155</v>
+        <v>2.602766864724846</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.1280496043929334</v>
+        <v>0.126079610479196</v>
       </c>
       <c r="W66">
-        <v>0.1280023180751174</v>
+        <v>0.128291513181654</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8536640292862228</v>
+        <v>0.8405307365279732</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1655977249653785</v>
+        <v>0.1666077249653785</v>
       </c>
       <c r="C67">
-        <v>2.206970102609368</v>
+        <v>1.934164494403056</v>
       </c>
       <c r="D67">
-        <v>9.278170102609369</v>
+        <v>9.209844494403056</v>
       </c>
       <c r="E67">
-        <v>12.6432</v>
+        <v>12.84768</v>
       </c>
       <c r="F67">
-        <v>13.2912</v>
+        <v>13.49568</v>
       </c>
       <c r="G67">
         <v>6.22</v>
@@ -6769,37 +6769,37 @@
         <v>1.64</v>
       </c>
       <c r="M67">
-        <v>1.95114816</v>
+        <v>1.981165824</v>
       </c>
       <c r="N67">
-        <v>-0.3111481600000003</v>
+        <v>-0.3411658240000004</v>
       </c>
       <c r="O67">
-        <v>-0.04667222400000005</v>
+        <v>-0.05117487360000006</v>
       </c>
       <c r="P67">
-        <v>-0.2644759360000003</v>
+        <v>-0.2899909504000003</v>
       </c>
       <c r="Q67">
-        <v>-0.1444759360000002</v>
+        <v>-0.1699909504000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.234880689706581</v>
+        <v>0.2404418864626569</v>
       </c>
       <c r="T67">
-        <v>2.602766864724846</v>
+        <v>2.6793188313344</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.126079610479196</v>
+        <v>0.1241693133507233</v>
       </c>
       <c r="W67">
-        <v>0.128291513181654</v>
+        <v>0.1285719448001138</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8405307365279732</v>
+        <v>0.8277954223381554</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1666077249653785</v>
+        <v>0.1676177249653785</v>
       </c>
       <c r="C68">
-        <v>1.934164494403056</v>
+        <v>1.662357846423372</v>
       </c>
       <c r="D68">
-        <v>9.209844494403056</v>
+        <v>9.142517846423374</v>
       </c>
       <c r="E68">
-        <v>12.84768</v>
+        <v>13.05216</v>
       </c>
       <c r="F68">
-        <v>13.49568</v>
+        <v>13.70016</v>
       </c>
       <c r="G68">
         <v>6.22</v>
@@ -6851,37 +6851,37 @@
         <v>1.64</v>
       </c>
       <c r="M68">
-        <v>1.981165824</v>
+        <v>2.011183488</v>
       </c>
       <c r="N68">
-        <v>-0.3411658240000004</v>
+        <v>-0.3711834880000004</v>
       </c>
       <c r="O68">
-        <v>-0.05117487360000006</v>
+        <v>-0.05567752320000006</v>
       </c>
       <c r="P68">
-        <v>-0.2899909504000003</v>
+        <v>-0.3155059648000004</v>
       </c>
       <c r="Q68">
-        <v>-0.1699909504000002</v>
+        <v>-0.1955059648000003</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2404418864626569</v>
+        <v>0.2463401254463738</v>
       </c>
       <c r="T68">
-        <v>2.6793188313344</v>
+        <v>2.760510311071807</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.1241693133507233</v>
+        <v>0.1223160400171304</v>
       </c>
       <c r="W68">
-        <v>0.1285719448001138</v>
+        <v>0.1288440053254853</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8277954223381554</v>
+        <v>0.8154402667808694</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1676177249653785</v>
+        <v>0.1686277249653785</v>
       </c>
       <c r="C69">
-        <v>1.662357846423372</v>
+        <v>1.391528409591061</v>
       </c>
       <c r="D69">
-        <v>9.142517846423374</v>
+        <v>9.076168409591061</v>
       </c>
       <c r="E69">
-        <v>13.05216</v>
+        <v>13.25664</v>
       </c>
       <c r="F69">
-        <v>13.70016</v>
+        <v>13.90464</v>
       </c>
       <c r="G69">
         <v>6.22</v>
@@ -6933,37 +6933,37 @@
         <v>1.64</v>
       </c>
       <c r="M69">
-        <v>2.011183488</v>
+        <v>2.041201152</v>
       </c>
       <c r="N69">
-        <v>-0.3711834880000004</v>
+        <v>-0.4012011520000003</v>
       </c>
       <c r="O69">
-        <v>-0.05567752320000006</v>
+        <v>-0.06018017280000004</v>
       </c>
       <c r="P69">
-        <v>-0.3155059648000004</v>
+        <v>-0.3410209792000002</v>
       </c>
       <c r="Q69">
-        <v>-0.1955059648000003</v>
+        <v>-0.2210209792000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2463401254463738</v>
+        <v>0.252607004366573</v>
       </c>
       <c r="T69">
-        <v>2.760510311071807</v>
+        <v>2.8467762582928</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.1223160400171304</v>
+        <v>0.1205172747227609</v>
       </c>
       <c r="W69">
-        <v>0.1288440053254853</v>
+        <v>0.1291080640706987</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8154402667808694</v>
+        <v>0.8034484981517391</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1686277249653785</v>
+        <v>0.208486410641777</v>
       </c>
       <c r="C70">
-        <v>1.391528409591061</v>
+        <v>-0.8336408645909401</v>
       </c>
       <c r="D70">
-        <v>9.076168409591061</v>
+        <v>7.055479135409061</v>
       </c>
       <c r="E70">
-        <v>13.25664</v>
+        <v>13.46112</v>
       </c>
       <c r="F70">
-        <v>13.90464</v>
+        <v>14.10912</v>
       </c>
       <c r="G70">
         <v>6.22</v>
@@ -7015,45 +7015,45 @@
         <v>1.64</v>
       </c>
       <c r="M70">
-        <v>2.041201152</v>
+        <v>2.833111296</v>
       </c>
       <c r="N70">
-        <v>-0.4012011520000003</v>
+        <v>-1.193111296</v>
       </c>
       <c r="O70">
-        <v>-0.06018017280000004</v>
+        <v>-0.1789666944</v>
       </c>
       <c r="P70">
-        <v>-0.3410209792000002</v>
+        <v>-1.0141446016</v>
       </c>
       <c r="Q70">
-        <v>-0.2210209792000001</v>
+        <v>-0.8941446016000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.252607004366573</v>
+        <v>0.2644029905603285</v>
       </c>
       <c r="T70">
-        <v>2.8467762582928</v>
+        <v>3.009152448317825</v>
       </c>
       <c r="U70">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1205172747227609</v>
+        <v>0.08683033396793176</v>
       </c>
       <c r="W70">
-        <v>0.1291080640706987</v>
+        <v>0.1833644689392393</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8034484981517391</v>
+        <v>0.578868893119545</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.208486410641777</v>
+        <v>0.210036410641777</v>
       </c>
       <c r="C71">
-        <v>-0.8336408645909401</v>
+        <v>-1.098681216641776</v>
       </c>
       <c r="D71">
-        <v>7.055479135409061</v>
+        <v>6.994918783358226</v>
       </c>
       <c r="E71">
-        <v>13.46112</v>
+        <v>13.6656</v>
       </c>
       <c r="F71">
-        <v>14.10912</v>
+        <v>14.3136</v>
       </c>
       <c r="G71">
         <v>6.22</v>
@@ -7097,37 +7097,37 @@
         <v>1.64</v>
       </c>
       <c r="M71">
-        <v>2.833111296</v>
+        <v>2.87417088</v>
       </c>
       <c r="N71">
-        <v>-1.193111296</v>
+        <v>-1.23417088</v>
       </c>
       <c r="O71">
-        <v>-0.1789666944</v>
+        <v>-0.1851256320000001</v>
       </c>
       <c r="P71">
-        <v>-1.0141446016</v>
+        <v>-1.049045248</v>
       </c>
       <c r="Q71">
-        <v>-0.8941446016000001</v>
+        <v>-0.9290452480000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2644029905603285</v>
+        <v>0.2716897569123394</v>
       </c>
       <c r="T71">
-        <v>3.009152448317825</v>
+        <v>3.109457529928419</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.08683033396793176</v>
+        <v>0.08558990062553272</v>
       </c>
       <c r="W71">
-        <v>0.1833644689392393</v>
+        <v>0.183613547954393</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.578868893119545</v>
+        <v>0.5705993375035515</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.210036410641777</v>
+        <v>0.2115864106417769</v>
       </c>
       <c r="C72">
-        <v>-1.098681216641776</v>
+        <v>-1.362690782889075</v>
       </c>
       <c r="D72">
-        <v>6.994918783358226</v>
+        <v>6.935389217110926</v>
       </c>
       <c r="E72">
-        <v>13.6656</v>
+        <v>13.87008</v>
       </c>
       <c r="F72">
-        <v>14.3136</v>
+        <v>14.51808</v>
       </c>
       <c r="G72">
         <v>6.22</v>
@@ -7179,37 +7179,37 @@
         <v>1.64</v>
       </c>
       <c r="M72">
-        <v>2.87417088</v>
+        <v>2.915230464</v>
       </c>
       <c r="N72">
-        <v>-1.23417088</v>
+        <v>-1.275230464000001</v>
       </c>
       <c r="O72">
-        <v>-0.1851256320000001</v>
+        <v>-0.1912845696000001</v>
       </c>
       <c r="P72">
-        <v>-1.049045248</v>
+        <v>-1.0839458944</v>
       </c>
       <c r="Q72">
-        <v>-0.9290452480000002</v>
+        <v>-0.9639458944000003</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2716897569123394</v>
+        <v>0.2794790588748339</v>
       </c>
       <c r="T72">
-        <v>3.109457529928419</v>
+        <v>3.216680203374227</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.08558990062553272</v>
+        <v>0.08438440906742664</v>
       </c>
       <c r="W72">
-        <v>0.183613547954393</v>
+        <v>0.1838556106592607</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5705993375035515</v>
+        <v>0.5625627271161775</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2115864106417769</v>
+        <v>0.213136410641777</v>
       </c>
       <c r="C73">
-        <v>-1.362690782889073</v>
+        <v>-1.625695658455557</v>
       </c>
       <c r="D73">
-        <v>6.935389217110926</v>
+        <v>6.876864341544443</v>
       </c>
       <c r="E73">
-        <v>13.87008</v>
+        <v>14.07456</v>
       </c>
       <c r="F73">
-        <v>14.51808</v>
+        <v>14.72256</v>
       </c>
       <c r="G73">
         <v>6.22</v>
@@ -7261,37 +7261,37 @@
         <v>1.64</v>
       </c>
       <c r="M73">
-        <v>2.915230464</v>
+        <v>2.956290048</v>
       </c>
       <c r="N73">
-        <v>-1.275230464</v>
+        <v>-1.316290048</v>
       </c>
       <c r="O73">
-        <v>-0.1912845696</v>
+        <v>-0.1974435072</v>
       </c>
       <c r="P73">
-        <v>-1.0839458944</v>
+        <v>-1.1188465408</v>
       </c>
       <c r="Q73">
-        <v>-0.9639458943999999</v>
+        <v>-0.9988465408</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2794790588748338</v>
+        <v>0.287824739548935</v>
       </c>
       <c r="T73">
-        <v>3.216680203374226</v>
+        <v>3.33156163920902</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.08438440906742664</v>
+        <v>0.08321240338593461</v>
       </c>
       <c r="W73">
-        <v>0.1838556106592607</v>
+        <v>0.1840909494001043</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5625627271161777</v>
+        <v>0.5547493559062306</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.213136410641777</v>
+        <v>0.2146864106417769</v>
       </c>
       <c r="C74">
-        <v>-1.625695658455557</v>
+        <v>-1.887721065010927</v>
       </c>
       <c r="D74">
-        <v>6.876864341544443</v>
+        <v>6.819318934989074</v>
       </c>
       <c r="E74">
-        <v>14.07456</v>
+        <v>14.27904</v>
       </c>
       <c r="F74">
-        <v>14.72256</v>
+        <v>14.92704</v>
       </c>
       <c r="G74">
         <v>6.22</v>
@@ -7343,37 +7343,37 @@
         <v>1.64</v>
       </c>
       <c r="M74">
-        <v>2.956290048</v>
+        <v>2.997349632</v>
       </c>
       <c r="N74">
-        <v>-1.316290048</v>
+        <v>-1.357349632</v>
       </c>
       <c r="O74">
-        <v>-0.1974435072</v>
+        <v>-0.2036024448</v>
       </c>
       <c r="P74">
-        <v>-1.1188465408</v>
+        <v>-1.1537471872</v>
       </c>
       <c r="Q74">
-        <v>-0.9988465408</v>
+        <v>-1.0337471872</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.287824739548935</v>
+        <v>0.2967886187914882</v>
       </c>
       <c r="T74">
-        <v>3.33156163920902</v>
+        <v>3.454952811031576</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.08321240338593461</v>
+        <v>0.08207250744914098</v>
       </c>
       <c r="W74">
-        <v>0.1840909494001043</v>
+        <v>0.1843198405042125</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5547493559062306</v>
+        <v>0.5471500496609398</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2146864106417769</v>
+        <v>0.2162364106417769</v>
       </c>
       <c r="C75">
-        <v>-1.887721065010927</v>
+        <v>-2.148791387013782</v>
       </c>
       <c r="D75">
-        <v>6.819318934989074</v>
+        <v>6.762728612986219</v>
       </c>
       <c r="E75">
-        <v>14.27904</v>
+        <v>14.48352</v>
       </c>
       <c r="F75">
-        <v>14.92704</v>
+        <v>15.13152</v>
       </c>
       <c r="G75">
         <v>6.22</v>
@@ -7425,37 +7425,37 @@
         <v>1.64</v>
       </c>
       <c r="M75">
-        <v>2.997349632</v>
+        <v>3.038409216</v>
       </c>
       <c r="N75">
-        <v>-1.357349632</v>
+        <v>-1.398409216</v>
       </c>
       <c r="O75">
-        <v>-0.2036024448</v>
+        <v>-0.2097613824000001</v>
       </c>
       <c r="P75">
-        <v>-1.1537471872</v>
+        <v>-1.1886478336</v>
       </c>
       <c r="Q75">
-        <v>-1.0337471872</v>
+        <v>-1.0686478336</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2967886187914882</v>
+        <v>0.3064420272065454</v>
       </c>
       <c r="T75">
-        <v>3.454952811031576</v>
+        <v>3.587835611455867</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.08207250744914098</v>
+        <v>0.08096341951063907</v>
       </c>
       <c r="W75">
-        <v>0.1843198405042125</v>
+        <v>0.1845425453622637</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5471500496609398</v>
+        <v>0.5397561300709272</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2162364106417769</v>
+        <v>0.2177864106417769</v>
       </c>
       <c r="C76">
-        <v>-2.148791387013782</v>
+        <v>-2.40893020616379</v>
       </c>
       <c r="D76">
-        <v>6.762728612986219</v>
+        <v>6.70706979383621</v>
       </c>
       <c r="E76">
-        <v>14.48352</v>
+        <v>14.688</v>
       </c>
       <c r="F76">
-        <v>15.13152</v>
+        <v>15.336</v>
       </c>
       <c r="G76">
         <v>6.22</v>
@@ -7507,37 +7507,37 @@
         <v>1.64</v>
       </c>
       <c r="M76">
-        <v>3.038409216</v>
+        <v>3.0794688</v>
       </c>
       <c r="N76">
-        <v>-1.398409216</v>
+        <v>-1.4394688</v>
       </c>
       <c r="O76">
-        <v>-0.2097613824000001</v>
+        <v>-0.2159203200000001</v>
       </c>
       <c r="P76">
-        <v>-1.1886478336</v>
+        <v>-1.22354848</v>
       </c>
       <c r="Q76">
-        <v>-1.0686478336</v>
+        <v>-1.10354848</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3064420272065454</v>
+        <v>0.3168677082948072</v>
       </c>
       <c r="T76">
-        <v>3.587835611455867</v>
+        <v>3.731349035914102</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.08096341951063907</v>
+        <v>0.07988390725049721</v>
       </c>
       <c r="W76">
-        <v>0.1845425453622637</v>
+        <v>0.1847593114241002</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5397561300709272</v>
+        <v>0.5325593816699814</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2177864106417769</v>
+        <v>0.2193364106417769</v>
       </c>
       <c r="C77">
-        <v>-2.40893020616379</v>
+        <v>-2.668160334166517</v>
       </c>
       <c r="D77">
-        <v>6.70706979383621</v>
+        <v>6.652319665833484</v>
       </c>
       <c r="E77">
-        <v>14.688</v>
+        <v>14.89248</v>
       </c>
       <c r="F77">
-        <v>15.336</v>
+        <v>15.54048</v>
       </c>
       <c r="G77">
         <v>6.22</v>
@@ -7589,37 +7589,37 @@
         <v>1.64</v>
       </c>
       <c r="M77">
-        <v>3.0794688</v>
+        <v>3.120528384</v>
       </c>
       <c r="N77">
-        <v>-1.4394688</v>
+        <v>-1.480528384</v>
       </c>
       <c r="O77">
-        <v>-0.2159203200000001</v>
+        <v>-0.2220792576</v>
       </c>
       <c r="P77">
-        <v>-1.22354848</v>
+        <v>-1.2584491264</v>
       </c>
       <c r="Q77">
-        <v>-1.10354848</v>
+        <v>-1.1384491264</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3168677082948072</v>
+        <v>0.3281621961404242</v>
       </c>
       <c r="T77">
-        <v>3.731349035914102</v>
+        <v>3.886821912410523</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.07988390725049721</v>
+        <v>0.07883280320772752</v>
       </c>
       <c r="W77">
-        <v>0.1847593114241002</v>
+        <v>0.1849703731158883</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5325593816699814</v>
+        <v>0.5255520213848501</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2193364106417769</v>
+        <v>0.2208864106417769</v>
       </c>
       <c r="C78">
-        <v>-2.668160334166517</v>
+        <v>-2.926503843906419</v>
       </c>
       <c r="D78">
-        <v>6.652319665833484</v>
+        <v>6.598456156093583</v>
       </c>
       <c r="E78">
-        <v>14.89248</v>
+        <v>15.09696</v>
       </c>
       <c r="F78">
-        <v>15.54048</v>
+        <v>15.74496</v>
       </c>
       <c r="G78">
         <v>6.22</v>
@@ -7671,37 +7671,37 @@
         <v>1.64</v>
       </c>
       <c r="M78">
-        <v>3.120528384</v>
+        <v>3.161587968</v>
       </c>
       <c r="N78">
-        <v>-1.480528384</v>
+        <v>-1.521587968</v>
       </c>
       <c r="O78">
-        <v>-0.2220792576</v>
+        <v>-0.2282381952</v>
       </c>
       <c r="P78">
-        <v>-1.2584491264</v>
+        <v>-1.2933497728</v>
       </c>
       <c r="Q78">
-        <v>-1.1384491264</v>
+        <v>-1.1733497728</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3281621961404242</v>
+        <v>0.340438813363921</v>
       </c>
       <c r="T78">
-        <v>3.886821912410523</v>
+        <v>4.055814169471851</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.07883280320772752</v>
+        <v>0.07780900056866613</v>
       </c>
       <c r="W78">
-        <v>0.1849703731158883</v>
+        <v>0.1851759526858119</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5255520213848501</v>
+        <v>0.5187266704577742</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2208864106417769</v>
+        <v>0.2224364106417769</v>
       </c>
       <c r="C79">
-        <v>-2.926503843906419</v>
+        <v>-3.183982099117612</v>
       </c>
       <c r="D79">
-        <v>6.598456156093583</v>
+        <v>6.54545790088239</v>
       </c>
       <c r="E79">
-        <v>15.09696</v>
+        <v>15.30144</v>
       </c>
       <c r="F79">
-        <v>15.74496</v>
+        <v>15.94944</v>
       </c>
       <c r="G79">
         <v>6.22</v>
@@ -7753,37 +7753,37 @@
         <v>1.64</v>
       </c>
       <c r="M79">
-        <v>3.161587968</v>
+        <v>3.202647552</v>
       </c>
       <c r="N79">
-        <v>-1.521587968</v>
+        <v>-1.562647552</v>
       </c>
       <c r="O79">
-        <v>-0.2282381952</v>
+        <v>-0.2343971328</v>
       </c>
       <c r="P79">
-        <v>-1.2933497728</v>
+        <v>-1.3282504192</v>
       </c>
       <c r="Q79">
-        <v>-1.1733497728</v>
+        <v>-1.2082504192</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.340438813363921</v>
+        <v>0.3538314866986447</v>
       </c>
       <c r="T79">
-        <v>4.055814169471851</v>
+        <v>4.240169358993299</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.07780900056866613</v>
+        <v>0.07681144927932425</v>
       </c>
       <c r="W79">
-        <v>0.1851759526858119</v>
+        <v>0.1853762609847117</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5187266704577742</v>
+        <v>0.5120763285288283</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2224364106417769</v>
+        <v>0.2239864106417769</v>
       </c>
       <c r="C80">
-        <v>-3.183982099117612</v>
+        <v>-3.440615782636137</v>
       </c>
       <c r="D80">
-        <v>6.54545790088239</v>
+        <v>6.493304217363863</v>
       </c>
       <c r="E80">
-        <v>15.30144</v>
+        <v>15.50592</v>
       </c>
       <c r="F80">
-        <v>15.94944</v>
+        <v>16.15392</v>
       </c>
       <c r="G80">
         <v>6.22</v>
@@ -7835,37 +7835,37 @@
         <v>1.64</v>
       </c>
       <c r="M80">
-        <v>3.202647552</v>
+        <v>3.243707136</v>
       </c>
       <c r="N80">
-        <v>-1.562647552</v>
+        <v>-1.603707136</v>
       </c>
       <c r="O80">
-        <v>-0.2343971328</v>
+        <v>-0.2405560704</v>
       </c>
       <c r="P80">
-        <v>-1.3282504192</v>
+        <v>-1.3631510656</v>
       </c>
       <c r="Q80">
-        <v>-1.2082504192</v>
+        <v>-1.2431510656</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3538314866986447</v>
+        <v>0.3684996527319134</v>
       </c>
       <c r="T80">
-        <v>4.240169358993299</v>
+        <v>4.442082185612027</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.07681144927932425</v>
+        <v>0.0758391524530037</v>
       </c>
       <c r="W80">
-        <v>0.1853762609847117</v>
+        <v>0.1855714981874369</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5120763285288283</v>
+        <v>0.5055943496866913</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2239864106417769</v>
+        <v>0.2541774645013987</v>
       </c>
       <c r="C81">
-        <v>-3.440615782636137</v>
+        <v>-4.517464580480725</v>
       </c>
       <c r="D81">
-        <v>6.493304217363863</v>
+        <v>5.620935419519275</v>
       </c>
       <c r="E81">
-        <v>15.50592</v>
+        <v>15.7104</v>
       </c>
       <c r="F81">
-        <v>16.15392</v>
+        <v>16.3584</v>
       </c>
       <c r="G81">
         <v>6.22</v>
@@ -7917,45 +7917,45 @@
         <v>1.64</v>
       </c>
       <c r="M81">
-        <v>3.243707136</v>
+        <v>3.85731072</v>
       </c>
       <c r="N81">
-        <v>-1.603707136</v>
+        <v>-2.21731072</v>
       </c>
       <c r="O81">
-        <v>-0.2405560704</v>
+        <v>-0.3325966080000001</v>
       </c>
       <c r="P81">
-        <v>-1.3631510656</v>
+        <v>-1.884714112</v>
       </c>
       <c r="Q81">
-        <v>-1.2431510656</v>
+        <v>-1.764714112</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3684996527319134</v>
+        <v>0.3878399046666177</v>
       </c>
       <c r="T81">
-        <v>4.442082185612027</v>
+        <v>4.708308033260429</v>
       </c>
       <c r="U81">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0758391524530037</v>
+        <v>0.06377500228967813</v>
       </c>
       <c r="W81">
-        <v>0.1855714981874369</v>
+        <v>0.2207618544600939</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.5055943496866913</v>
+        <v>0.4251666819311875</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2541774645013987</v>
+        <v>0.2560774645013987</v>
       </c>
       <c r="C82">
-        <v>-4.517464580480725</v>
+        <v>-4.769070713642432</v>
       </c>
       <c r="D82">
-        <v>5.620935419519275</v>
+        <v>5.573809286357569</v>
       </c>
       <c r="E82">
-        <v>15.7104</v>
+        <v>15.91488</v>
       </c>
       <c r="F82">
-        <v>16.3584</v>
+        <v>16.56288</v>
       </c>
       <c r="G82">
         <v>6.22</v>
@@ -7999,37 +7999,37 @@
         <v>1.64</v>
       </c>
       <c r="M82">
-        <v>3.85731072</v>
+        <v>3.905527104</v>
       </c>
       <c r="N82">
-        <v>-2.21731072</v>
+        <v>-2.265527104</v>
       </c>
       <c r="O82">
-        <v>-0.3325966080000001</v>
+        <v>-0.3398290656</v>
       </c>
       <c r="P82">
-        <v>-1.884714112</v>
+        <v>-1.9256980384</v>
       </c>
       <c r="Q82">
-        <v>-1.764714112</v>
+        <v>-1.8056980384</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3878399046666177</v>
+        <v>0.4058420049122292</v>
       </c>
       <c r="T82">
-        <v>4.708308033260429</v>
+        <v>4.956113719221505</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06377500228967813</v>
+        <v>0.06298765658239815</v>
       </c>
       <c r="W82">
-        <v>0.2207618544600939</v>
+        <v>0.2209475105778705</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4251666819311875</v>
+        <v>0.4199177105493209</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2560774645013987</v>
+        <v>0.2579774645013987</v>
       </c>
       <c r="C83">
-        <v>-4.769070713642432</v>
+        <v>-5.019893202376098</v>
       </c>
       <c r="D83">
-        <v>5.573809286357569</v>
+        <v>5.527466797623902</v>
       </c>
       <c r="E83">
-        <v>15.91488</v>
+        <v>16.11936</v>
       </c>
       <c r="F83">
-        <v>16.56288</v>
+        <v>16.76736</v>
       </c>
       <c r="G83">
         <v>6.22</v>
@@ -8081,37 +8081,37 @@
         <v>1.64</v>
       </c>
       <c r="M83">
-        <v>3.905527104</v>
+        <v>3.953743488</v>
       </c>
       <c r="N83">
-        <v>-2.265527104</v>
+        <v>-2.313743488</v>
       </c>
       <c r="O83">
-        <v>-0.3398290656</v>
+        <v>-0.3470615232</v>
       </c>
       <c r="P83">
-        <v>-1.9256980384</v>
+        <v>-1.9666819648</v>
       </c>
       <c r="Q83">
-        <v>-1.8056980384</v>
+        <v>-1.8466819648</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4058420049122292</v>
+        <v>0.4258443385184641</v>
       </c>
       <c r="T83">
-        <v>4.956113719221505</v>
+        <v>5.231453370289366</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06298765658239815</v>
+        <v>0.06221951442895426</v>
       </c>
       <c r="W83">
-        <v>0.2209475105778705</v>
+        <v>0.2211286384976526</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4199177105493209</v>
+        <v>0.4147967628596951</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2579774645013987</v>
+        <v>0.2598774645013987</v>
       </c>
       <c r="C84">
-        <v>-5.019893202376098</v>
+        <v>-5.269951431940981</v>
       </c>
       <c r="D84">
-        <v>5.527466797623902</v>
+        <v>5.481888568059019</v>
       </c>
       <c r="E84">
-        <v>16.11936</v>
+        <v>16.32384</v>
       </c>
       <c r="F84">
-        <v>16.76736</v>
+        <v>16.97184</v>
       </c>
       <c r="G84">
         <v>6.22</v>
@@ -8163,37 +8163,37 @@
         <v>1.64</v>
       </c>
       <c r="M84">
-        <v>3.953743488</v>
+        <v>4.001959872</v>
       </c>
       <c r="N84">
-        <v>-2.313743488</v>
+        <v>-2.361959872000001</v>
       </c>
       <c r="O84">
-        <v>-0.3470615232</v>
+        <v>-0.3542939808000001</v>
       </c>
       <c r="P84">
-        <v>-1.9666819648</v>
+        <v>-2.007665891200001</v>
       </c>
       <c r="Q84">
-        <v>-1.8466819648</v>
+        <v>-1.887665891200001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4258443385184641</v>
+        <v>0.4481998878430797</v>
       </c>
       <c r="T84">
-        <v>5.231453370289366</v>
+        <v>5.539185921482859</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06221951442895426</v>
+        <v>0.06146988172499095</v>
       </c>
       <c r="W84">
-        <v>0.2211286384976526</v>
+        <v>0.2213054018892472</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4147967628596951</v>
+        <v>0.4097992114999397</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2598774645013987</v>
+        <v>0.2617774645013987</v>
       </c>
       <c r="C85">
-        <v>-5.269951431940981</v>
+        <v>-5.519264153439757</v>
       </c>
       <c r="D85">
-        <v>5.481888568059019</v>
+        <v>5.437055846560243</v>
       </c>
       <c r="E85">
-        <v>16.32384</v>
+        <v>16.52832</v>
       </c>
       <c r="F85">
-        <v>16.97184</v>
+        <v>17.17632</v>
       </c>
       <c r="G85">
         <v>6.22</v>
@@ -8245,37 +8245,37 @@
         <v>1.64</v>
       </c>
       <c r="M85">
-        <v>4.001959872</v>
+        <v>4.050176256</v>
       </c>
       <c r="N85">
-        <v>-2.361959872000001</v>
+        <v>-2.410176256000001</v>
       </c>
       <c r="O85">
-        <v>-0.3542939808000001</v>
+        <v>-0.3615264384000001</v>
       </c>
       <c r="P85">
-        <v>-2.007665891200001</v>
+        <v>-2.0486498176</v>
       </c>
       <c r="Q85">
-        <v>-1.887665891200001</v>
+        <v>-1.9286498176</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4481998878430797</v>
+        <v>0.4733498808332723</v>
       </c>
       <c r="T85">
-        <v>5.539185921482859</v>
+        <v>5.885385041575538</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06146988172499095</v>
+        <v>0.06073809741874106</v>
       </c>
       <c r="W85">
-        <v>0.2213054018892472</v>
+        <v>0.2214779566286609</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4097992114999397</v>
+        <v>0.4049206494582738</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2617774645013987</v>
+        <v>0.2636774645013986</v>
       </c>
       <c r="C86">
-        <v>-5.519264153439757</v>
+        <v>-5.767849509539891</v>
       </c>
       <c r="D86">
-        <v>5.437055846560243</v>
+        <v>5.39295049046011</v>
       </c>
       <c r="E86">
-        <v>16.52832</v>
+        <v>16.7328</v>
       </c>
       <c r="F86">
-        <v>17.17632</v>
+        <v>17.3808</v>
       </c>
       <c r="G86">
         <v>6.22</v>
@@ -8327,37 +8327,37 @@
         <v>1.64</v>
       </c>
       <c r="M86">
-        <v>4.050176256</v>
+        <v>4.09839264</v>
       </c>
       <c r="N86">
-        <v>-2.410176256000001</v>
+        <v>-2.45839264</v>
       </c>
       <c r="O86">
-        <v>-0.3615264384000001</v>
+        <v>-0.3687588960000001</v>
       </c>
       <c r="P86">
-        <v>-2.0486498176</v>
+        <v>-2.089633744</v>
       </c>
       <c r="Q86">
-        <v>-1.9286498176</v>
+        <v>-1.969633744</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.473349880833272</v>
+        <v>0.5018532062221568</v>
       </c>
       <c r="T86">
-        <v>5.885385041575534</v>
+        <v>6.277744044347237</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06073809741874106</v>
+        <v>0.06002353156675588</v>
       </c>
       <c r="W86">
-        <v>0.2214779566286609</v>
+        <v>0.221646451256559</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4049206494582738</v>
+        <v>0.4001568771117058</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2636774645013986</v>
+        <v>0.2655774645013986</v>
       </c>
       <c r="C87">
-        <v>-5.767849509539891</v>
+        <v>-6.015725058953159</v>
       </c>
       <c r="D87">
-        <v>5.39295049046011</v>
+        <v>5.349554941046843</v>
       </c>
       <c r="E87">
-        <v>16.7328</v>
+        <v>16.93728</v>
       </c>
       <c r="F87">
-        <v>17.3808</v>
+        <v>17.58528</v>
       </c>
       <c r="G87">
         <v>6.22</v>
@@ -8409,37 +8409,37 @@
         <v>1.64</v>
       </c>
       <c r="M87">
-        <v>4.09839264</v>
+        <v>4.146609024</v>
       </c>
       <c r="N87">
-        <v>-2.45839264</v>
+        <v>-2.506609024</v>
       </c>
       <c r="O87">
-        <v>-0.3687588960000001</v>
+        <v>-0.3759913536</v>
       </c>
       <c r="P87">
-        <v>-2.089633744</v>
+        <v>-2.1306176704</v>
       </c>
       <c r="Q87">
-        <v>-1.969633744</v>
+        <v>-2.0106176704</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5018532062221568</v>
+        <v>0.5344284352380252</v>
       </c>
       <c r="T87">
-        <v>6.277744044347237</v>
+        <v>6.726154333229182</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.06002353156675588</v>
+        <v>0.05932558352528198</v>
       </c>
       <c r="W87">
-        <v>0.221646451256559</v>
+        <v>0.2218110274047385</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4001568771117058</v>
+        <v>0.3955038901685465</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2655774645013986</v>
+        <v>0.2674774645013986</v>
       </c>
       <c r="C88">
-        <v>-6.015725058953159</v>
+        <v>-6.262907799742742</v>
       </c>
       <c r="D88">
-        <v>5.349554941046843</v>
+        <v>5.306852200257259</v>
       </c>
       <c r="E88">
-        <v>16.93728</v>
+        <v>17.14176</v>
       </c>
       <c r="F88">
-        <v>17.58528</v>
+        <v>17.78976</v>
       </c>
       <c r="G88">
         <v>6.22</v>
@@ -8491,37 +8491,37 @@
         <v>1.64</v>
       </c>
       <c r="M88">
-        <v>4.146609024</v>
+        <v>4.194825408000001</v>
       </c>
       <c r="N88">
-        <v>-2.506609024</v>
+        <v>-2.554825408000001</v>
       </c>
       <c r="O88">
-        <v>-0.3759913536</v>
+        <v>-0.3832238112000002</v>
       </c>
       <c r="P88">
-        <v>-2.1306176704</v>
+        <v>-2.171601596800001</v>
       </c>
       <c r="Q88">
-        <v>-2.0106176704</v>
+        <v>-2.051601596800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5344284352380252</v>
+        <v>0.5720152379486424</v>
       </c>
       <c r="T88">
-        <v>6.726154333229182</v>
+        <v>7.243550820400658</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05932558352528198</v>
+        <v>0.05864368026637068</v>
       </c>
       <c r="W88">
-        <v>0.2218110274047385</v>
+        <v>0.2219718201931898</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3955038901685465</v>
+        <v>0.3909578684424712</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2674774645013986</v>
+        <v>0.2693774645013987</v>
       </c>
       <c r="C89">
-        <v>-6.262907799742742</v>
+        <v>-6.509414191522861</v>
       </c>
       <c r="D89">
-        <v>5.306852200257259</v>
+        <v>5.264825808477141</v>
       </c>
       <c r="E89">
-        <v>17.14176</v>
+        <v>17.34624</v>
       </c>
       <c r="F89">
-        <v>17.78976</v>
+        <v>17.99424</v>
       </c>
       <c r="G89">
         <v>6.22</v>
@@ -8573,37 +8573,37 @@
         <v>1.64</v>
       </c>
       <c r="M89">
-        <v>4.194825408000001</v>
+        <v>4.243041792000001</v>
       </c>
       <c r="N89">
-        <v>-2.554825408000001</v>
+        <v>-2.603041792000001</v>
       </c>
       <c r="O89">
-        <v>-0.3832238112000002</v>
+        <v>-0.3904562688000001</v>
       </c>
       <c r="P89">
-        <v>-2.171601596800001</v>
+        <v>-2.212585523200001</v>
       </c>
       <c r="Q89">
-        <v>-2.051601596800001</v>
+        <v>-2.092585523200001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5720152379486424</v>
+        <v>0.615866507777696</v>
       </c>
       <c r="T89">
-        <v>7.243550820400658</v>
+        <v>7.847180055434047</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05864368026637068</v>
+        <v>0.05797727480879829</v>
       </c>
       <c r="W89">
-        <v>0.2219718201931898</v>
+        <v>0.2221289586000854</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3909578684424712</v>
+        <v>0.3865151653919886</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2693774645013987</v>
+        <v>0.2712774645013987</v>
       </c>
       <c r="C90">
-        <v>-6.509414191522861</v>
+        <v>-6.75526017661187</v>
       </c>
       <c r="D90">
-        <v>5.264825808477141</v>
+        <v>5.223459823388131</v>
       </c>
       <c r="E90">
-        <v>17.34624</v>
+        <v>17.55072</v>
       </c>
       <c r="F90">
-        <v>17.99424</v>
+        <v>18.19872</v>
       </c>
       <c r="G90">
         <v>6.22</v>
@@ -8655,37 +8655,37 @@
         <v>1.64</v>
       </c>
       <c r="M90">
-        <v>4.243041792000001</v>
+        <v>4.291258176</v>
       </c>
       <c r="N90">
-        <v>-2.603041792000001</v>
+        <v>-2.651258176000001</v>
       </c>
       <c r="O90">
-        <v>-0.3904562688000001</v>
+        <v>-0.3976887264000001</v>
       </c>
       <c r="P90">
-        <v>-2.212585523200001</v>
+        <v>-2.2535694496</v>
       </c>
       <c r="Q90">
-        <v>-2.092585523200001</v>
+        <v>-2.1335694496</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.615866507777696</v>
+        <v>0.6676907357574866</v>
       </c>
       <c r="T90">
-        <v>7.847180055434047</v>
+        <v>8.560560060473506</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05797727480879829</v>
+        <v>0.05732584475476685</v>
       </c>
       <c r="W90">
-        <v>0.2221289586000854</v>
+        <v>0.222282565806826</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3865151653919886</v>
+        <v>0.3821722983651122</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2712774645013987</v>
+        <v>0.2731774645013987</v>
       </c>
       <c r="C91">
-        <v>-6.75526017661187</v>
+        <v>-7.000461200195925</v>
       </c>
       <c r="D91">
-        <v>5.223459823388131</v>
+        <v>5.182738799804078</v>
       </c>
       <c r="E91">
-        <v>17.55072</v>
+        <v>17.7552</v>
       </c>
       <c r="F91">
-        <v>18.19872</v>
+        <v>18.4032</v>
       </c>
       <c r="G91">
         <v>6.22</v>
@@ -8737,37 +8737,37 @@
         <v>1.64</v>
       </c>
       <c r="M91">
-        <v>4.291258176</v>
+        <v>4.33947456</v>
       </c>
       <c r="N91">
-        <v>-2.651258176000001</v>
+        <v>-2.699474560000001</v>
       </c>
       <c r="O91">
-        <v>-0.3976887264000001</v>
+        <v>-0.404921184</v>
       </c>
       <c r="P91">
-        <v>-2.2535694496</v>
+        <v>-2.294553376000001</v>
       </c>
       <c r="Q91">
-        <v>-2.1335694496</v>
+        <v>-2.174553376</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6676907357574866</v>
+        <v>0.7298798093332354</v>
       </c>
       <c r="T91">
-        <v>8.560560060473506</v>
+        <v>9.416616066520858</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05732584475476685</v>
+        <v>0.05668889092415833</v>
       </c>
       <c r="W91">
-        <v>0.222282565806826</v>
+        <v>0.2224327595200835</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3821722983651122</v>
+        <v>0.3779259394943888</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2731774645013987</v>
+        <v>0.2750774645013986</v>
       </c>
       <c r="C92">
-        <v>-7.000461200195925</v>
+        <v>-7.245032229556777</v>
       </c>
       <c r="D92">
-        <v>5.182738799804078</v>
+        <v>5.142647770443225</v>
       </c>
       <c r="E92">
-        <v>17.7552</v>
+        <v>17.95968</v>
       </c>
       <c r="F92">
-        <v>18.4032</v>
+        <v>18.60768</v>
       </c>
       <c r="G92">
         <v>6.22</v>
@@ -8819,37 +8819,37 @@
         <v>1.64</v>
       </c>
       <c r="M92">
-        <v>4.33947456</v>
+        <v>4.387690944000001</v>
       </c>
       <c r="N92">
-        <v>-2.699474560000001</v>
+        <v>-2.747690944000001</v>
       </c>
       <c r="O92">
-        <v>-0.404921184</v>
+        <v>-0.4121536416000002</v>
       </c>
       <c r="P92">
-        <v>-2.294553376000001</v>
+        <v>-2.335537302400001</v>
       </c>
       <c r="Q92">
-        <v>-2.174553376</v>
+        <v>-2.215537302400001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7298798093332354</v>
+        <v>0.8058886770369282</v>
       </c>
       <c r="T92">
-        <v>9.416616066520858</v>
+        <v>10.46290674057873</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05668889092415833</v>
+        <v>0.05606593607883791</v>
       </c>
       <c r="W92">
-        <v>0.2224327595200835</v>
+        <v>0.22257965227261</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3779259394943888</v>
+        <v>0.3737729071922526</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2750774645013986</v>
+        <v>0.2769774645013987</v>
       </c>
       <c r="C93">
-        <v>-7.245032229556777</v>
+        <v>-7.488987772414037</v>
       </c>
       <c r="D93">
-        <v>5.142647770443225</v>
+        <v>5.103172227585966</v>
       </c>
       <c r="E93">
-        <v>17.95968</v>
+        <v>18.16416</v>
       </c>
       <c r="F93">
-        <v>18.60768</v>
+        <v>18.81216</v>
       </c>
       <c r="G93">
         <v>6.22</v>
@@ -8901,37 +8901,37 @@
         <v>1.64</v>
       </c>
       <c r="M93">
-        <v>4.387690944000001</v>
+        <v>4.435907328000001</v>
       </c>
       <c r="N93">
-        <v>-2.747690944000001</v>
+        <v>-2.795907328000001</v>
       </c>
       <c r="O93">
-        <v>-0.4121536416000002</v>
+        <v>-0.4193860992000001</v>
       </c>
       <c r="P93">
-        <v>-2.335537302400001</v>
+        <v>-2.376521228800001</v>
       </c>
       <c r="Q93">
-        <v>-2.215537302400001</v>
+        <v>-2.256521228800001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8058886770369282</v>
+        <v>0.9008997616665445</v>
       </c>
       <c r="T93">
-        <v>10.46290674057873</v>
+        <v>11.77077008315108</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05606593607883791</v>
+        <v>0.05545652373015488</v>
       </c>
       <c r="W93">
-        <v>0.22257965227261</v>
+        <v>0.2227233517044295</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3737729071922526</v>
+        <v>0.3697101582010325</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2769774645013987</v>
+        <v>0.2788774645013987</v>
       </c>
       <c r="C94">
-        <v>-7.488987772414037</v>
+        <v>-7.732341894429041</v>
       </c>
       <c r="D94">
-        <v>5.103172227585966</v>
+        <v>5.064298105570961</v>
       </c>
       <c r="E94">
-        <v>18.16416</v>
+        <v>18.36864</v>
       </c>
       <c r="F94">
-        <v>18.81216</v>
+        <v>19.01664</v>
       </c>
       <c r="G94">
         <v>6.22</v>
@@ -8983,37 +8983,37 @@
         <v>1.64</v>
       </c>
       <c r="M94">
-        <v>4.435907328000001</v>
+        <v>4.484123712000001</v>
       </c>
       <c r="N94">
-        <v>-2.795907328000001</v>
+        <v>-2.844123712000001</v>
       </c>
       <c r="O94">
-        <v>-0.4193860992000001</v>
+        <v>-0.4266185568000001</v>
       </c>
       <c r="P94">
-        <v>-2.376521228800001</v>
+        <v>-2.417505155200001</v>
       </c>
       <c r="Q94">
-        <v>-2.256521228800001</v>
+        <v>-2.297505155200001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9008997616665445</v>
+        <v>1.023056870476051</v>
       </c>
       <c r="T94">
-        <v>11.77077008315108</v>
+        <v>13.45230866645838</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05545652373015488</v>
+        <v>0.05486021702337903</v>
       </c>
       <c r="W94">
-        <v>0.2227233517044295</v>
+        <v>0.2228639608258872</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3697101582010325</v>
+        <v>0.3657347801558601</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2788774645013987</v>
+        <v>0.2807774645013987</v>
       </c>
       <c r="C95">
-        <v>-7.732341894429041</v>
+        <v>-7.975108235914782</v>
       </c>
       <c r="D95">
-        <v>5.064298105570961</v>
+        <v>5.026011764085221</v>
       </c>
       <c r="E95">
-        <v>18.36864</v>
+        <v>18.57312</v>
       </c>
       <c r="F95">
-        <v>19.01664</v>
+        <v>19.22112</v>
       </c>
       <c r="G95">
         <v>6.22</v>
@@ -9065,37 +9065,37 @@
         <v>1.64</v>
       </c>
       <c r="M95">
-        <v>4.484123712000001</v>
+        <v>4.532340096</v>
       </c>
       <c r="N95">
-        <v>-2.844123712000001</v>
+        <v>-2.892340096000001</v>
       </c>
       <c r="O95">
-        <v>-0.4266185568000001</v>
+        <v>-0.4338510144000001</v>
       </c>
       <c r="P95">
-        <v>-2.417505155200001</v>
+        <v>-2.458489081600001</v>
       </c>
       <c r="Q95">
-        <v>-2.297505155200001</v>
+        <v>-2.338489081600001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.023056870476051</v>
+        <v>1.185933015555393</v>
       </c>
       <c r="T95">
-        <v>13.45230866645838</v>
+        <v>15.69436011086811</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05486021702337903</v>
+        <v>0.05427659769334308</v>
       </c>
       <c r="W95">
-        <v>0.2228639608258872</v>
+        <v>0.2230015782639097</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3657347801558601</v>
+        <v>0.3618439846222872</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2807774645013987</v>
+        <v>0.2826774645013986</v>
       </c>
       <c r="C96">
-        <v>-7.975108235914782</v>
+        <v>-8.217300027793524</v>
       </c>
       <c r="D96">
-        <v>5.026011764085221</v>
+        <v>4.98829997220648</v>
       </c>
       <c r="E96">
-        <v>18.57312</v>
+        <v>18.7776</v>
       </c>
       <c r="F96">
-        <v>19.22112</v>
+        <v>19.4256</v>
       </c>
       <c r="G96">
         <v>6.22</v>
@@ -9147,37 +9147,37 @@
         <v>1.64</v>
       </c>
       <c r="M96">
-        <v>4.532340096</v>
+        <v>4.580556480000001</v>
       </c>
       <c r="N96">
-        <v>-2.892340096000001</v>
+        <v>-2.940556480000001</v>
       </c>
       <c r="O96">
-        <v>-0.4338510144000001</v>
+        <v>-0.4410834720000002</v>
       </c>
       <c r="P96">
-        <v>-2.458489081600001</v>
+        <v>-2.499473008000001</v>
       </c>
       <c r="Q96">
-        <v>-2.338489081600001</v>
+        <v>-2.379473008000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.185933015555393</v>
+        <v>1.413959618666472</v>
       </c>
       <c r="T96">
-        <v>15.69436011086811</v>
+        <v>18.83323213304174</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05427659769334308</v>
+        <v>0.05370526508604473</v>
       </c>
       <c r="W96">
-        <v>0.2230015782639097</v>
+        <v>0.2231362984927107</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3618439846222872</v>
+        <v>0.3580351005736314</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2826774645013986</v>
+        <v>0.2845774645013987</v>
       </c>
       <c r="C97">
-        <v>-8.217300027793524</v>
+        <v>-8.45893010684139</v>
       </c>
       <c r="D97">
-        <v>4.98829997220648</v>
+        <v>4.951149893158615</v>
       </c>
       <c r="E97">
-        <v>18.7776</v>
+        <v>18.98208</v>
       </c>
       <c r="F97">
-        <v>19.4256</v>
+        <v>19.63008</v>
       </c>
       <c r="G97">
         <v>6.22</v>
@@ -9229,37 +9229,37 @@
         <v>1.64</v>
       </c>
       <c r="M97">
-        <v>4.580556480000001</v>
+        <v>4.628772864000001</v>
       </c>
       <c r="N97">
-        <v>-2.940556480000001</v>
+        <v>-2.988772864000001</v>
       </c>
       <c r="O97">
-        <v>-0.4410834720000002</v>
+        <v>-0.4483159296000002</v>
       </c>
       <c r="P97">
-        <v>-2.499473008000001</v>
+        <v>-2.540456934400001</v>
       </c>
       <c r="Q97">
-        <v>-2.379473008000001</v>
+        <v>-2.420456934400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.413959618666472</v>
+        <v>1.755999523333092</v>
       </c>
       <c r="T97">
-        <v>18.83323213304174</v>
+        <v>23.54154016630218</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05370526508604473</v>
+        <v>0.05314583524139842</v>
       </c>
       <c r="W97">
-        <v>0.2231362984927107</v>
+        <v>0.2232682120500783</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3580351005736314</v>
+        <v>0.3543055682759895</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2845774645013986</v>
+        <v>0.2864774645013987</v>
       </c>
       <c r="C98">
-        <v>-8.458930106841382</v>
+        <v>-8.70001093025674</v>
       </c>
       <c r="D98">
-        <v>4.951149893158618</v>
+        <v>4.91454906974326</v>
       </c>
       <c r="E98">
-        <v>18.98208</v>
+        <v>19.18656</v>
       </c>
       <c r="F98">
-        <v>19.63008</v>
+        <v>19.83456</v>
       </c>
       <c r="G98">
         <v>6.22</v>
@@ -9311,37 +9311,37 @@
         <v>1.64</v>
       </c>
       <c r="M98">
-        <v>4.628772864</v>
+        <v>4.676989248</v>
       </c>
       <c r="N98">
-        <v>-2.988772864</v>
+        <v>-3.036989248</v>
       </c>
       <c r="O98">
-        <v>-0.4483159296000001</v>
+        <v>-0.4555483872</v>
       </c>
       <c r="P98">
-        <v>-2.5404569344</v>
+        <v>-2.5814408608</v>
       </c>
       <c r="Q98">
-        <v>-2.4204569344</v>
+        <v>-2.4614408608</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.755999523333087</v>
+        <v>2.326066031110782</v>
       </c>
       <c r="T98">
-        <v>23.54154016630212</v>
+        <v>31.38872022173616</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05314583524139844</v>
+        <v>0.05259794003272423</v>
       </c>
       <c r="W98">
-        <v>0.2232682120500782</v>
+        <v>0.2233974057402836</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3543055682759896</v>
+        <v>0.3506529335514948</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2864774645013987</v>
+        <v>0.2883774645013986</v>
       </c>
       <c r="C99">
-        <v>-8.70001093025674</v>
+        <v>-8.940554589587201</v>
       </c>
       <c r="D99">
-        <v>4.91454906974326</v>
+        <v>4.878485410412798</v>
       </c>
       <c r="E99">
-        <v>19.18656</v>
+        <v>19.39104</v>
       </c>
       <c r="F99">
-        <v>19.83456</v>
+        <v>20.03904</v>
       </c>
       <c r="G99">
         <v>6.22</v>
@@ -9393,37 +9393,37 @@
         <v>1.64</v>
       </c>
       <c r="M99">
-        <v>4.676989248</v>
+        <v>4.725205632</v>
       </c>
       <c r="N99">
-        <v>-3.036989248</v>
+        <v>-3.085205632</v>
       </c>
       <c r="O99">
-        <v>-0.4555483872</v>
+        <v>-0.4627808448</v>
       </c>
       <c r="P99">
-        <v>-2.5814408608</v>
+        <v>-2.6224247872</v>
       </c>
       <c r="Q99">
-        <v>-2.4614408608</v>
+        <v>-2.5024247872</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.326066031110782</v>
+        <v>3.466199046666173</v>
       </c>
       <c r="T99">
-        <v>31.38872022173616</v>
+        <v>47.08308033260423</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05259794003272423</v>
+        <v>0.05206122635892092</v>
       </c>
       <c r="W99">
-        <v>0.2233974057402836</v>
+        <v>0.2235239628245664</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3506529335514948</v>
+        <v>0.3470748423928061</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2883774645013986</v>
+        <v>0.2902774645013986</v>
       </c>
       <c r="C100">
-        <v>-8.940554589587201</v>
+        <v>-9.180572824047863</v>
       </c>
       <c r="D100">
-        <v>4.878485410412798</v>
+        <v>4.842947175952138</v>
       </c>
       <c r="E100">
-        <v>19.39104</v>
+        <v>19.59552</v>
       </c>
       <c r="F100">
-        <v>20.03904</v>
+        <v>20.24352</v>
       </c>
       <c r="G100">
         <v>6.22</v>
@@ -9475,37 +9475,37 @@
         <v>1.64</v>
       </c>
       <c r="M100">
-        <v>4.725205632</v>
+        <v>4.773422016</v>
       </c>
       <c r="N100">
-        <v>-3.085205632</v>
+        <v>-3.133422016000001</v>
       </c>
       <c r="O100">
-        <v>-0.4627808448</v>
+        <v>-0.4700133024000001</v>
       </c>
       <c r="P100">
-        <v>-2.6224247872</v>
+        <v>-2.663408713600001</v>
       </c>
       <c r="Q100">
-        <v>-2.5024247872</v>
+        <v>-2.543408713600001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.466199046666173</v>
+        <v>6.886598093332347</v>
       </c>
       <c r="T100">
-        <v>47.08308033260423</v>
+        <v>94.16616066520848</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05206122635892092</v>
+        <v>0.05153535538559847</v>
       </c>
       <c r="W100">
-        <v>0.2235239628245664</v>
+        <v>0.2236479632000759</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3470748423928061</v>
+        <v>0.3435690359039898</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2902774645013986</v>
-      </c>
-      <c r="C101">
-        <v>-9.180572824047863</v>
-      </c>
-      <c r="D101">
-        <v>4.842947175952138</v>
-      </c>
-      <c r="E101">
-        <v>19.59552</v>
-      </c>
-      <c r="F101">
-        <v>20.24352</v>
-      </c>
-      <c r="G101">
-        <v>6.22</v>
-      </c>
-      <c r="H101">
-        <v>19.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.76</v>
-      </c>
-      <c r="K101">
-        <v>0.1200000000000001</v>
-      </c>
-      <c r="L101">
-        <v>1.64</v>
-      </c>
-      <c r="M101">
-        <v>4.773422016</v>
-      </c>
-      <c r="N101">
-        <v>-3.133422016000001</v>
-      </c>
-      <c r="O101">
-        <v>-0.4700133024000001</v>
-      </c>
-      <c r="P101">
-        <v>-2.663408713600001</v>
-      </c>
-      <c r="Q101">
-        <v>-2.543408713600001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.886598093332347</v>
-      </c>
-      <c r="T101">
-        <v>94.16616066520848</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05153535538559847</v>
-      </c>
-      <c r="W101">
-        <v>0.2236479632000759</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3435690359039898</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
